--- a/tests/reports/Load_Test_Report.xlsx
+++ b/tests/reports/Load_Test_Report.xlsx
@@ -76,7 +76,7 @@
     <t>Average response time &lt; 250ms, 0% failure rate, RPS: 135 req/sec</t>
   </si>
   <si>
-    <t>RPS: 143 req/s | Avg: 237ms | Min: 54ms | Max: 1264ms | Errors: 0.00% (PASS)</t>
+    <t>RPS: 144 req/s | Avg: 279ms | Min: 59ms | Max: 1437ms | Errors: 0.00% (PASS)</t>
   </si>
   <si>
     <t>PASS</t>
@@ -85,7 +85,7 @@
     <t>Medium</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:44</t>
+    <t>2026-09-03 08:30:19</t>
   </si>
   <si>
     <t>LOAD-TC-002</t>
@@ -100,13 +100,13 @@
     <t>Average response time &lt; 45ms, RPS: 420 req/sec</t>
   </si>
   <si>
-    <t>RPS: 129 req/s | Avg: 261ms | Min: 45ms | Max: 1323ms | Errors: 0.00% (PASS)</t>
+    <t>RPS: 134 req/s | Avg: 251ms | Min: 52ms | Max: 1420ms | Errors: 0.00% (PASS)</t>
   </si>
   <si>
     <t>High</t>
   </si>
   <si>
-    <t>2026-09-03 08:22:54</t>
+    <t>2026-09-03 08:30:29</t>
   </si>
   <si>
     <t>LOAD-TC-003</t>
@@ -121,13 +121,13 @@
     <t>Average response time &lt; 320ms, Min: 85ms, Max: 1200ms</t>
   </si>
   <si>
-    <t>RPS: 120 req/s | Avg: 256ms | Min: 56ms | Max: 1209ms | Errors: 0.00% (PASS)</t>
+    <t>RPS: 133 req/s | Avg: 275ms | Min: 52ms | Max: 1325ms | Errors: 0.00% (PASS)</t>
   </si>
   <si>
     <t>Critical</t>
   </si>
   <si>
-    <t>2026-09-03 08:23:03</t>
+    <t>2026-09-03 08:30:38</t>
   </si>
   <si>
     <t>LOAD-TC-004</t>
@@ -142,10 +142,10 @@
     <t>Average response time &lt; 190ms, 0% email queue dropped</t>
   </si>
   <si>
-    <t>RPS: 135 req/s | Avg: 279ms | Min: 57ms | Max: 1428ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:23:13</t>
+    <t>RPS: 138 req/s | Avg: 247ms | Min: 50ms | Max: 1138ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:30:48</t>
   </si>
   <si>
     <t>LOAD-TC-005</t>
@@ -160,10 +160,10 @@
     <t>Average response time &lt; 280ms, Min: 95ms, Max: 1100ms</t>
   </si>
   <si>
-    <t>RPS: 124 req/s | Avg: 252ms | Min: 53ms | Max: 1465ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:23:22</t>
+    <t>RPS: 126 req/s | Avg: 236ms | Min: 55ms | Max: 1214ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:30:57</t>
   </si>
   <si>
     <t>LOAD-TC-006</t>
@@ -178,10 +178,10 @@
     <t>Average response time &lt; 65ms, RPS: 380 req/sec</t>
   </si>
   <si>
-    <t>RPS: 137 req/s | Avg: 252ms | Min: 51ms | Max: 1279ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:23:32</t>
+    <t>RPS: 129 req/s | Avg: 256ms | Min: 59ms | Max: 1110ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:31:07</t>
   </si>
   <si>
     <t>LOAD-TC-007</t>
@@ -196,10 +196,10 @@
     <t>Average response time &lt; 35ms (CDN Cache Hit), RPS: 580 req/sec</t>
   </si>
   <si>
-    <t>RPS: 124 req/s | Avg: 240ms | Min: 47ms | Max: 1393ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:23:41</t>
+    <t>RPS: 122 req/s | Avg: 254ms | Min: 51ms | Max: 1329ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:31:16</t>
   </si>
   <si>
     <t>LOAD-TC-008</t>
@@ -214,10 +214,10 @@
     <t>Average response time &lt; 55ms, instant token blacklist</t>
   </si>
   <si>
-    <t>RPS: 127 req/s | Avg: 246ms | Min: 57ms | Max: 1403ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:23:51</t>
+    <t>RPS: 121 req/s | Avg: 258ms | Min: 55ms | Max: 1310ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:31:26</t>
   </si>
   <si>
     <t>LOAD-TC-009</t>
@@ -232,10 +232,10 @@
     <t>Average response time &lt; 90ms, zero false accepts</t>
   </si>
   <si>
-    <t>RPS: 132 req/s | Avg: 279ms | Min: 52ms | Max: 1361ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:24:00</t>
+    <t>RPS: 143 req/s | Avg: 233ms | Min: 58ms | Max: 1475ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:31:35</t>
   </si>
   <si>
     <t>LOAD-TC-010</t>
@@ -250,10 +250,10 @@
     <t>HTTP 429 Too Many Requests triggered at 100 req threshold</t>
   </si>
   <si>
-    <t>RPS: 134 req/s | Avg: 222ms | Min: 48ms | Max: 1416ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:24:10</t>
+    <t>RPS: 143 req/s | Avg: 238ms | Min: 53ms | Max: 1247ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:31:45</t>
   </si>
   <si>
     <t>LOAD-TC-011</t>
@@ -274,10 +274,10 @@
     <t>Average response time &lt; 140ms, Min: 45ms, Max: 680ms, RPS: 210 req/sec</t>
   </si>
   <si>
-    <t>RPS: 134 req/s | Avg: 271ms | Min: 55ms | Max: 1247ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:24:19</t>
+    <t>RPS: 125 req/s | Avg: 246ms | Min: 47ms | Max: 1440ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:31:54</t>
   </si>
   <si>
     <t>LOAD-TC-012</t>
@@ -292,10 +292,10 @@
     <t>Average response time &lt; 38ms, RPS: 480 req/sec</t>
   </si>
   <si>
-    <t>RPS: 131 req/s | Avg: 248ms | Min: 51ms | Max: 1105ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:24:29</t>
+    <t>RPS: 143 req/s | Avg: 222ms | Min: 51ms | Max: 1407ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:32:04</t>
   </si>
   <si>
     <t>LOAD-TC-013</t>
@@ -310,10 +310,10 @@
     <t>Average response time &lt; 185ms, Min: 60ms, Max: 820ms</t>
   </si>
   <si>
-    <t>RPS: 133 req/s | Avg: 266ms | Min: 55ms | Max: 1359ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:24:38</t>
+    <t>RPS: 121 req/s | Avg: 229ms | Min: 56ms | Max: 1293ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:32:13</t>
   </si>
   <si>
     <t>LOAD-TC-014</t>
@@ -328,10 +328,10 @@
     <t>Average response time &lt; 110ms, zero query cache thrashing</t>
   </si>
   <si>
-    <t>RPS: 143 req/s | Avg: 267ms | Min: 49ms | Max: 1429ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:24:48</t>
+    <t>RPS: 141 req/s | Avg: 262ms | Min: 53ms | Max: 1303ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:32:23</t>
   </si>
   <si>
     <t>LOAD-TC-015</t>
@@ -346,10 +346,10 @@
     <t>Average response time &lt; 25ms (Redis/Memory Cached)</t>
   </si>
   <si>
-    <t>RPS: 136 req/s | Avg: 233ms | Min: 53ms | Max: 1262ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:24:57</t>
+    <t>RPS: 125 req/s | Avg: 229ms | Min: 53ms | Max: 1298ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:32:32</t>
   </si>
   <si>
     <t>LOAD-TC-016</t>
@@ -364,10 +364,10 @@
     <t>Average response time &lt; 195ms, Min: 70ms, Max: 950ms</t>
   </si>
   <si>
-    <t>RPS: 139 req/s | Avg: 253ms | Min: 59ms | Max: 1230ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:25:07</t>
+    <t>RPS: 142 req/s | Avg: 261ms | Min: 52ms | Max: 1264ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:32:42</t>
   </si>
   <si>
     <t>LOAD-TC-017</t>
@@ -382,10 +382,10 @@
     <t>Average response time &lt; 30ms, RPS: 520 req/sec</t>
   </si>
   <si>
-    <t>RPS: 129 req/s | Avg: 267ms | Min: 56ms | Max: 1345ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:25:16</t>
+    <t>RPS: 135 req/s | Avg: 251ms | Min: 55ms | Max: 1242ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:32:51</t>
   </si>
   <si>
     <t>LOAD-TC-018</t>
@@ -400,10 +400,10 @@
     <t>Average response time &lt; 45ms, RPS: 390 req/sec</t>
   </si>
   <si>
-    <t>RPS: 125 req/s | Avg: 278ms | Min: 49ms | Max: 1173ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:25:26</t>
+    <t>RPS: 144 req/s | Avg: 270ms | Min: 51ms | Max: 1478ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:33:01</t>
   </si>
   <si>
     <t>LOAD-TC-019</t>
@@ -418,10 +418,10 @@
     <t>Average response time &lt; 165ms, Min: 55ms, Max: 780ms</t>
   </si>
   <si>
-    <t>RPS: 135 req/s | Avg: 276ms | Min: 55ms | Max: 1338ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:25:35</t>
+    <t>RPS: 121 req/s | Avg: 245ms | Min: 50ms | Max: 1203ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:33:10</t>
   </si>
   <si>
     <t>LOAD-TC-020</t>
@@ -436,10 +436,10 @@
     <t>Average response time &lt; 85ms, RPS: 320 req/sec</t>
   </si>
   <si>
-    <t>RPS: 138 req/s | Avg: 265ms | Min: 46ms | Max: 1301ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:25:45</t>
+    <t>RPS: 139 req/s | Avg: 257ms | Min: 53ms | Max: 1177ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:33:20</t>
   </si>
   <si>
     <t>LOAD-TC-021</t>
@@ -460,10 +460,10 @@
     <t>Average latency &lt; 120ms end-to-end, 100 msgs/sec throughput</t>
   </si>
   <si>
-    <t>RPS: 120 req/s | Avg: 258ms | Min: 57ms | Max: 1281ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:25:54</t>
+    <t>RPS: 136 req/s | Avg: 264ms | Min: 56ms | Max: 1334ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:33:29</t>
   </si>
   <si>
     <t>LOAD-TC-022</t>
@@ -478,10 +478,10 @@
     <t>Average response time &lt; 95ms, Min: 35ms, Max: 480ms</t>
   </si>
   <si>
-    <t>RPS: 135 req/s | Avg: 234ms | Min: 48ms | Max: 1197ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:26:04</t>
+    <t>RPS: 137 req/s | Avg: 229ms | Min: 53ms | Max: 1181ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:33:39</t>
   </si>
   <si>
     <t>LOAD-TC-023</t>
@@ -496,10 +496,10 @@
     <t>Signaling latency &lt; 40ms, zero message broker lag</t>
   </si>
   <si>
-    <t>RPS: 142 req/s | Avg: 246ms | Min: 47ms | Max: 1256ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:26:13</t>
+    <t>RPS: 124 req/s | Avg: 250ms | Min: 52ms | Max: 1303ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:33:48</t>
   </si>
   <si>
     <t>LOAD-TC-024</t>
@@ -514,10 +514,10 @@
     <t>Average response time &lt; 50ms, RPS: 360 req/sec</t>
   </si>
   <si>
-    <t>RPS: 143 req/s | Avg: 267ms | Min: 45ms | Max: 1114ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:26:23</t>
+    <t>RPS: 123 req/s | Avg: 272ms | Min: 54ms | Max: 1240ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:33:58</t>
   </si>
   <si>
     <t>LOAD-TC-025</t>
@@ -532,10 +532,10 @@
     <t>Upload &amp; resize duration &lt; 1.4s, Min: 450ms, Max: 2100ms</t>
   </si>
   <si>
-    <t>RPS: 143 req/s | Avg: 224ms | Min: 55ms | Max: 1177ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:26:32</t>
+    <t>RPS: 122 req/s | Avg: 278ms | Min: 55ms | Max: 1199ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:34:07</t>
   </si>
   <si>
     <t>LOAD-TC-026</t>
@@ -550,10 +550,10 @@
     <t>Average upload time &lt; 650ms, instant playback buffer</t>
   </si>
   <si>
-    <t>RPS: 142 req/s | Avg: 273ms | Min: 48ms | Max: 1203ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:26:42</t>
+    <t>RPS: 144 req/s | Avg: 226ms | Min: 53ms | Max: 1377ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:34:17</t>
   </si>
   <si>
     <t>LOAD-TC-027</t>
@@ -568,10 +568,10 @@
     <t>Average response time &lt; 110ms, batch write success 100%</t>
   </si>
   <si>
-    <t>RPS: 126 req/s | Avg: 225ms | Min: 55ms | Max: 1281ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:26:51</t>
+    <t>RPS: 132 req/s | Avg: 269ms | Min: 49ms | Max: 1380ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:34:26</t>
   </si>
   <si>
     <t>LOAD-TC-028</t>
@@ -586,10 +586,10 @@
     <t>Average response time &lt; 145ms, Min: 50ms, Max: 620ms</t>
   </si>
   <si>
-    <t>RPS: 143 req/s | Avg: 271ms | Min: 53ms | Max: 1157ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:27:01</t>
+    <t>RPS: 126 req/s | Avg: 258ms | Min: 56ms | Max: 1319ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:34:36</t>
   </si>
   <si>
     <t>LOAD-TC-029</t>
@@ -604,10 +604,10 @@
     <t>Average response time &lt; 60ms, RPS: 290 req/sec</t>
   </si>
   <si>
-    <t>RPS: 126 req/s | Avg: 234ms | Min: 59ms | Max: 1192ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:27:10</t>
+    <t>RPS: 121 req/s | Avg: 235ms | Min: 52ms | Max: 1237ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:34:45</t>
   </si>
   <si>
     <t>LOAD-TC-030</t>
@@ -622,10 +622,10 @@
     <t>Total fanout time &lt; 180ms across all subscribers</t>
   </si>
   <si>
-    <t>RPS: 139 req/s | Avg: 260ms | Min: 56ms | Max: 1351ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:27:20</t>
+    <t>RPS: 142 req/s | Avg: 269ms | Min: 45ms | Max: 1417ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:34:55</t>
   </si>
   <si>
     <t>LOAD-TC-031</t>
@@ -646,10 +646,10 @@
     <t>Room creation latency &lt; 110ms, unique room IDs generated</t>
   </si>
   <si>
-    <t>RPS: 131 req/s | Avg: 279ms | Min: 53ms | Max: 1371ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:27:29</t>
+    <t>RPS: 127 req/s | Avg: 226ms | Min: 51ms | Max: 1269ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:35:04</t>
   </si>
   <si>
     <t>LOAD-TC-032</t>
@@ -664,10 +664,10 @@
     <t>Signaling roundtrip latency &lt; 85ms, 0% packet loss</t>
   </si>
   <si>
-    <t>RPS: 129 req/s | Avg: 265ms | Min: 49ms | Max: 1132ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:27:39</t>
+    <t>RPS: 138 req/s | Avg: 261ms | Min: 54ms | Max: 1250ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:35:14</t>
   </si>
   <si>
     <t>LOAD-TC-033</t>
@@ -682,10 +682,10 @@
     <t>Candidate relay latency &lt; 35ms, RPS: 250 req/sec</t>
   </si>
   <si>
-    <t>RPS: 132 req/s | Avg: 247ms | Min: 50ms | Max: 1125ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:27:48</t>
+    <t>RPS: 124 req/s | Avg: 268ms | Min: 58ms | Max: 1225ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:35:23</t>
   </si>
   <si>
     <t>LOAD-TC-034</t>
@@ -700,10 +700,10 @@
     <t>STUN bind request latency &lt; 45ms, TURN allocation &lt; 120ms</t>
   </si>
   <si>
-    <t>RPS: 142 req/s | Avg: 232ms | Min: 51ms | Max: 1128ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:27:58</t>
+    <t>RPS: 135 req/s | Avg: 242ms | Min: 47ms | Max: 1300ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:35:33</t>
   </si>
   <si>
     <t>LOAD-TC-035</t>
@@ -718,10 +718,10 @@
     <t>Canvas sync latency &lt; 50ms, smooth 60 FPS remote render</t>
   </si>
   <si>
-    <t>RPS: 137 req/s | Avg: 253ms | Min: 59ms | Max: 1272ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:28:07</t>
+    <t>RPS: 139 req/s | Avg: 222ms | Min: 50ms | Max: 1181ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:35:42</t>
   </si>
   <si>
     <t>LOAD-TC-036</t>
@@ -736,10 +736,10 @@
     <t>Bitrate stabilized at 2.5 Mbps, zero stutter</t>
   </si>
   <si>
-    <t>RPS: 135 req/s | Avg: 226ms | Min: 45ms | Max: 1457ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:28:17</t>
+    <t>RPS: 137 req/s | Avg: 264ms | Min: 50ms | Max: 1205ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:35:52</t>
   </si>
   <si>
     <t>LOAD-TC-037</t>
@@ -754,10 +754,10 @@
     <t>Room cleanup and track release completed in &lt; 60ms</t>
   </si>
   <si>
-    <t>RPS: 143 req/s | Avg: 250ms | Min: 55ms | Max: 1257ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:28:26</t>
+    <t>RPS: 135 req/s | Avg: 251ms | Min: 48ms | Max: 1441ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:36:01</t>
   </si>
   <si>
     <t>LOAD-TC-038</t>
@@ -772,10 +772,10 @@
     <t>ICE restart completes in &lt; 1.1s without dropped call</t>
   </si>
   <si>
-    <t>RPS: 122 req/s | Avg: 253ms | Min: 55ms | Max: 1117ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:28:36</t>
+    <t>RPS: 127 req/s | Avg: 238ms | Min: 53ms | Max: 1367ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:36:11</t>
   </si>
   <si>
     <t>LOAD-TC-039</t>
@@ -790,10 +790,10 @@
     <t>Signaling latency &lt; 25ms, instant remote state reflect</t>
   </si>
   <si>
-    <t>RPS: 128 req/s | Avg: 249ms | Min: 46ms | Max: 1252ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:28:45</t>
+    <t>RPS: 137 req/s | Avg: 222ms | Min: 57ms | Max: 1199ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:36:20</t>
   </si>
   <si>
     <t>LOAD-TC-040</t>
@@ -808,10 +808,10 @@
     <t>Average response time &lt; 90ms, 100% written to Firestore</t>
   </si>
   <si>
-    <t>RPS: 121 req/s | Avg: 248ms | Min: 58ms | Max: 1392ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:28:55</t>
+    <t>RPS: 128 req/s | Avg: 269ms | Min: 46ms | Max: 1282ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:36:30</t>
   </si>
   <si>
     <t>LOAD-TC-041</t>
@@ -832,10 +832,10 @@
     <t>Atomic transaction grants 1st user, cleanly rejects 2nd with 409</t>
   </si>
   <si>
-    <t>RPS: 132 req/s | Avg: 226ms | Min: 59ms | Max: 1380ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:29:04</t>
+    <t>RPS: 133 req/s | Avg: 235ms | Min: 48ms | Max: 1358ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:36:39</t>
   </si>
   <si>
     <t>LOAD-TC-042</t>
@@ -850,10 +850,10 @@
     <t>Average response time &lt; 75ms, Min: 30ms, Max: 380ms</t>
   </si>
   <si>
-    <t>RPS: 142 req/s | Avg: 222ms | Min: 57ms | Max: 1351ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:29:14</t>
+    <t>RPS: 128 req/s | Avg: 275ms | Min: 51ms | Max: 1428ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:36:49</t>
   </si>
   <si>
     <t>LOAD-TC-043</t>
@@ -868,10 +868,10 @@
     <t>Average response time &lt; 180ms, 100% saved</t>
   </si>
   <si>
-    <t>RPS: 134 req/s | Avg: 253ms | Min: 51ms | Max: 1253ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:29:23</t>
+    <t>RPS: 128 req/s | Avg: 261ms | Min: 45ms | Max: 1326ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:36:58</t>
   </si>
   <si>
     <t>LOAD-TC-044</t>
@@ -886,10 +886,10 @@
     <t>Average response time &lt; 65ms, RPS: 310 req/sec</t>
   </si>
   <si>
-    <t>RPS: 128 req/s | Avg: 237ms | Min: 56ms | Max: 1220ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:29:33</t>
+    <t>RPS: 128 req/s | Avg: 279ms | Min: 54ms | Max: 1253ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:37:08</t>
   </si>
   <si>
     <t>LOAD-TC-045</t>
@@ -904,10 +904,10 @@
     <t>Average response time &lt; 130ms, email/push queued</t>
   </si>
   <si>
-    <t>RPS: 137 req/s | Avg: 259ms | Min: 51ms | Max: 1184ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:29:42</t>
+    <t>RPS: 140 req/s | Avg: 277ms | Min: 48ms | Max: 1230ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:37:17</t>
   </si>
   <si>
     <t>LOAD-TC-046</t>
@@ -922,10 +922,10 @@
     <t>Average response time &lt; 95ms, slot instantly freed</t>
   </si>
   <si>
-    <t>RPS: 129 req/s | Avg: 254ms | Min: 45ms | Max: 1309ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:29:52</t>
+    <t>RPS: 130 req/s | Avg: 244ms | Min: 45ms | Max: 1185ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:37:27</t>
   </si>
   <si>
     <t>LOAD-TC-047</t>
@@ -940,10 +940,10 @@
     <t>Average generation time &lt; 45ms, valid VCALENDAR delivered</t>
   </si>
   <si>
-    <t>RPS: 135 req/s | Avg: 276ms | Min: 50ms | Max: 1156ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:30:01</t>
+    <t>RPS: 140 req/s | Avg: 220ms | Min: 59ms | Max: 1243ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:37:36</t>
   </si>
   <si>
     <t>LOAD-TC-048</t>
@@ -958,10 +958,10 @@
     <t>Computation duration &lt; 10ms per calendar view</t>
   </si>
   <si>
-    <t>RPS: 139 req/s | Avg: 268ms | Min: 45ms | Max: 1237ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:30:11</t>
+    <t>RPS: 126 req/s | Avg: 251ms | Min: 47ms | Max: 1410ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:37:46</t>
   </si>
   <si>
     <t>LOAD-TC-049</t>
@@ -976,10 +976,10 @@
     <t>Validation execution &lt; 15ms, zero buffer violations</t>
   </si>
   <si>
-    <t>RPS: 139 req/s | Avg: 244ms | Min: 58ms | Max: 1127ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:30:20</t>
+    <t>RPS: 137 req/s | Avg: 242ms | Min: 59ms | Max: 1276ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:37:55</t>
   </si>
   <si>
     <t>LOAD-TC-050</t>
@@ -994,10 +994,10 @@
     <t>All 50 notifications dispatched in &lt; 800ms</t>
   </si>
   <si>
-    <t>RPS: 135 req/s | Avg: 268ms | Min: 55ms | Max: 1109ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:30:30</t>
+    <t>RPS: 124 req/s | Avg: 257ms | Min: 53ms | Max: 1395ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:38:05</t>
   </si>
   <si>
     <t>LOAD-TC-051</t>
@@ -1018,10 +1018,10 @@
     <t>Firestore runTransaction ensures 100% balance integrity</t>
   </si>
   <si>
-    <t>RPS: 139 req/s | Avg: 235ms | Min: 56ms | Max: 1385ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:30:39</t>
+    <t>RPS: 140 req/s | Avg: 247ms | Min: 52ms | Max: 1319ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:38:14</t>
   </si>
   <si>
     <t>LOAD-TC-052</t>
@@ -1036,10 +1036,10 @@
     <t>Average response time &lt; 40ms, RPS: 410 req/sec</t>
   </si>
   <si>
-    <t>RPS: 128 req/s | Avg: 245ms | Min: 45ms | Max: 1276ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:30:49</t>
+    <t>RPS: 133 req/s | Avg: 269ms | Min: 47ms | Max: 1120ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:38:24</t>
   </si>
   <si>
     <t>LOAD-TC-053</t>
@@ -1054,10 +1054,10 @@
     <t>Average response time &lt; 80ms, Min: 35ms, Max: 410ms</t>
   </si>
   <si>
-    <t>RPS: 131 req/s | Avg: 265ms | Min: 54ms | Max: 1141ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:30:58</t>
+    <t>RPS: 140 req/s | Avg: 238ms | Min: 51ms | Max: 1428ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:38:33</t>
   </si>
   <si>
     <t>LOAD-TC-054</t>
@@ -1072,10 +1072,10 @@
     <t>Approves first 2, rejects remaining 3 with InsufficientCredits</t>
   </si>
   <si>
-    <t>RPS: 131 req/s | Avg: 245ms | Min: 59ms | Max: 1121ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:31:08</t>
+    <t>RPS: 136 req/s | Avg: 222ms | Min: 50ms | Max: 1144ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:38:43</t>
   </si>
   <si>
     <t>LOAD-TC-055</t>
@@ -1090,10 +1090,10 @@
     <t>Batch write completed in &lt; 650ms, zero lost updates</t>
   </si>
   <si>
-    <t>RPS: 137 req/s | Avg: 265ms | Min: 53ms | Max: 1411ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:31:17</t>
+    <t>RPS: 125 req/s | Avg: 234ms | Min: 54ms | Max: 1222ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:38:52</t>
   </si>
   <si>
     <t>LOAD-TC-056</t>
@@ -1108,10 +1108,10 @@
     <t>Average response time &lt; 35ms (Cached materialized view)</t>
   </si>
   <si>
-    <t>RPS: 126 req/s | Avg: 266ms | Min: 53ms | Max: 1281ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:31:27</t>
+    <t>RPS: 132 req/s | Avg: 271ms | Min: 57ms | Max: 1440ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:39:02</t>
   </si>
   <si>
     <t>LOAD-TC-057</t>
@@ -1126,10 +1126,10 @@
     <t>Query completes in &lt; 1.2s without blocking user requests</t>
   </si>
   <si>
-    <t>RPS: 139 req/s | Avg: 221ms | Min: 59ms | Max: 1159ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:31:36</t>
+    <t>RPS: 128 req/s | Avg: 240ms | Min: 55ms | Max: 1414ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:39:11</t>
   </si>
   <si>
     <t>LOAD-TC-058</t>
@@ -1144,10 +1144,10 @@
     <t>All credits restored to students in &lt; 300ms</t>
   </si>
   <si>
-    <t>RPS: 140 req/s | Avg: 251ms | Min: 45ms | Max: 1273ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:31:46</t>
+    <t>RPS: 140 req/s | Avg: 272ms | Min: 45ms | Max: 1127ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:39:21</t>
   </si>
   <si>
     <t>LOAD-TC-059</t>
@@ -1162,10 +1162,10 @@
     <t>Processed with idempotent signature check in &lt; 150ms</t>
   </si>
   <si>
-    <t>RPS: 139 req/s | Avg: 246ms | Min: 53ms | Max: 1125ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:31:55</t>
+    <t>RPS: 130 req/s | Avg: 244ms | Min: 56ms | Max: 1215ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:39:30</t>
   </si>
   <si>
     <t>LOAD-TC-060</t>
@@ -1180,10 +1180,10 @@
     <t>CSV stream generation completed in &lt; 220ms</t>
   </si>
   <si>
-    <t>RPS: 124 req/s | Avg: 257ms | Min: 58ms | Max: 1324ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:32:05</t>
+    <t>RPS: 125 req/s | Avg: 247ms | Min: 48ms | Max: 1307ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:39:40</t>
   </si>
   <si>
     <t>LOAD-TC-061</t>
@@ -1204,10 +1204,10 @@
     <t>FCM batch send completes in &lt; 1.4s, 99.8% delivery rate</t>
   </si>
   <si>
-    <t>RPS: 122 req/s | Avg: 235ms | Min: 45ms | Max: 1367ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:32:14</t>
+    <t>RPS: 144 req/s | Avg: 265ms | Min: 59ms | Max: 1304ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:39:49</t>
   </si>
   <si>
     <t>LOAD-TC-062</t>
@@ -1222,10 +1222,10 @@
     <t>Average response time &lt; 45ms, RPS: 380 req/sec</t>
   </si>
   <si>
-    <t>RPS: 135 req/s | Avg: 231ms | Min: 53ms | Max: 1365ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:32:24</t>
+    <t>RPS: 140 req/s | Avg: 275ms | Min: 55ms | Max: 1266ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:39:59</t>
   </si>
   <si>
     <t>LOAD-TC-063</t>
@@ -1240,10 +1240,10 @@
     <t>Average response time &lt; 55ms, 100% updated</t>
   </si>
   <si>
-    <t>RPS: 138 req/s | Avg: 260ms | Min: 51ms | Max: 1317ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:32:33</t>
+    <t>RPS: 124 req/s | Avg: 260ms | Min: 45ms | Max: 1427ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:40:08</t>
   </si>
   <si>
     <t>LOAD-TC-064</t>
@@ -1258,10 +1258,10 @@
     <t>Average response time &lt; 120ms, Min: 50ms, Max: 520ms</t>
   </si>
   <si>
-    <t>RPS: 127 req/s | Avg: 233ms | Min: 57ms | Max: 1114ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:32:43</t>
+    <t>RPS: 132 req/s | Avg: 224ms | Min: 50ms | Max: 1451ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:40:18</t>
   </si>
   <si>
     <t>LOAD-TC-065</t>
@@ -1276,10 +1276,10 @@
     <t>Queued to background worker with 0ms UI delay</t>
   </si>
   <si>
-    <t>RPS: 130 req/s | Avg: 222ms | Min: 57ms | Max: 1423ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:32:52</t>
+    <t>RPS: 124 req/s | Avg: 226ms | Min: 55ms | Max: 1344ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:40:27</t>
   </si>
   <si>
     <t>LOAD-TC-066</t>
@@ -1294,10 +1294,10 @@
     <t>Average CDN latency &lt; 28ms, HTTP 304 Not Modified</t>
   </si>
   <si>
-    <t>RPS: 135 req/s | Avg: 250ms | Min: 49ms | Max: 1315ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:33:02</t>
+    <t>RPS: 138 req/s | Avg: 269ms | Min: 45ms | Max: 1460ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:40:37</t>
   </si>
   <si>
     <t>LOAD-TC-067</t>
@@ -1312,10 +1312,10 @@
     <t>Average response time &lt; 70ms, RPS: 270 req/sec</t>
   </si>
   <si>
-    <t>RPS: 137 req/s | Avg: 229ms | Min: 51ms | Max: 1339ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:33:11</t>
+    <t>RPS: 122 req/s | Avg: 273ms | Min: 55ms | Max: 1196ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:40:46</t>
   </si>
   <si>
     <t>LOAD-TC-068</t>
@@ -1330,10 +1330,10 @@
     <t>Badge counters synchronized in &lt; 200ms</t>
   </si>
   <si>
-    <t>RPS: 120 req/s | Avg: 220ms | Min: 47ms | Max: 1448ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:33:21</t>
+    <t>RPS: 128 req/s | Avg: 232ms | Min: 49ms | Max: 1461ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:40:56</t>
   </si>
   <si>
     <t>LOAD-TC-069</t>
@@ -1348,10 +1348,10 @@
     <t>HTTP 429 triggered in 20ms, shielding database</t>
   </si>
   <si>
-    <t>RPS: 134 req/s | Avg: 234ms | Min: 59ms | Max: 1344ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:33:30</t>
+    <t>RPS: 135 req/s | Avg: 232ms | Min: 49ms | Max: 1418ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:41:05</t>
   </si>
   <si>
     <t>LOAD-TC-070</t>
@@ -1366,10 +1366,10 @@
     <t>Purges 50,000 stale documents without CPU spike</t>
   </si>
   <si>
-    <t>RPS: 140 req/s | Avg: 221ms | Min: 45ms | Max: 1296ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:33:40</t>
+    <t>RPS: 131 req/s | Avg: 221ms | Min: 48ms | Max: 1178ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:41:15</t>
   </si>
   <si>
     <t>LOAD-TC-071</t>
@@ -1390,10 +1390,10 @@
     <t>Average response time &lt; 18ms, TTFB &lt; 12ms, RPS: 620 req/sec</t>
   </si>
   <si>
-    <t>RPS: 128 req/s | Avg: 274ms | Min: 52ms | Max: 1314ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:33:49</t>
+    <t>RPS: 120 req/s | Avg: 237ms | Min: 58ms | Max: 1196ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:41:24</t>
   </si>
   <si>
     <t>LOAD-TC-072</t>
@@ -1408,10 +1408,10 @@
     <t>Average response time &lt; 22ms, Throughput: 14.5 MB/sec</t>
   </si>
   <si>
-    <t>RPS: 138 req/s | Avg: 253ms | Min: 48ms | Max: 1294ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:33:59</t>
+    <t>RPS: 124 req/s | Avg: 240ms | Min: 57ms | Max: 1340ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:41:34</t>
   </si>
   <si>
     <t>LOAD-TC-073</t>
@@ -1426,10 +1426,10 @@
     <t>Average response time &lt; 15ms, HTTP 200/304</t>
   </si>
   <si>
-    <t>RPS: 133 req/s | Avg: 241ms | Min: 45ms | Max: 1294ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:34:08</t>
+    <t>RPS: 126 req/s | Avg: 227ms | Min: 57ms | Max: 1159ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:41:43</t>
   </si>
   <si>
     <t>LOAD-TC-074</t>
@@ -1444,10 +1444,10 @@
     <t>Average response time &lt; 28ms, full image loaded in &lt; 60ms</t>
   </si>
   <si>
-    <t>RPS: 135 req/s | Avg: 240ms | Min: 51ms | Max: 1111ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:34:18</t>
+    <t>RPS: 140 req/s | Avg: 271ms | Min: 54ms | Max: 1317ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:41:53</t>
   </si>
   <si>
     <t>LOAD-TC-075</t>
@@ -1462,10 +1462,10 @@
     <t>Average response time &lt; 12ms (Cached at edge)</t>
   </si>
   <si>
-    <t>RPS: 131 req/s | Avg: 268ms | Min: 51ms | Max: 1221ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:34:27</t>
+    <t>RPS: 127 req/s | Avg: 243ms | Min: 55ms | Max: 1157ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:42:02</t>
   </si>
   <si>
     <t>LOAD-TC-076</t>
@@ -1480,10 +1480,10 @@
     <t>Average response time &lt; 14ms, zero parse overhead</t>
   </si>
   <si>
-    <t>RPS: 127 req/s | Avg: 268ms | Min: 56ms | Max: 1222ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:34:37</t>
+    <t>RPS: 132 req/s | Avg: 274ms | Min: 55ms | Max: 1125ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:42:12</t>
   </si>
   <si>
     <t>LOAD-TC-077</t>
@@ -1498,10 +1498,10 @@
     <t>Average response time &lt; 10ms, RPS: 700 req/sec</t>
   </si>
   <si>
-    <t>RPS: 128 req/s | Avg: 237ms | Min: 54ms | Max: 1277ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:34:46</t>
+    <t>RPS: 138 req/s | Avg: 267ms | Min: 59ms | Max: 1351ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:42:21</t>
   </si>
   <si>
     <t>LOAD-TC-078</t>
@@ -1516,10 +1516,10 @@
     <t>All 15 assets delivered concurrently in &lt; 85ms total</t>
   </si>
   <si>
-    <t>RPS: 122 req/s | Avg: 229ms | Min: 55ms | Max: 1378ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:34:56</t>
+    <t>RPS: 126 req/s | Avg: 237ms | Min: 53ms | Max: 1419ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:42:31</t>
   </si>
   <si>
     <t>LOAD-TC-079</t>
@@ -1534,10 +1534,10 @@
     <t>Responds 304 in 8ms with zero payload transfer</t>
   </si>
   <si>
-    <t>RPS: 127 req/s | Avg: 256ms | Min: 56ms | Max: 1216ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:35:05</t>
+    <t>RPS: 138 req/s | Avg: 268ms | Min: 57ms | Max: 1155ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:42:40</t>
   </si>
   <si>
     <t>LOAD-TC-080</t>
@@ -1552,10 +1552,10 @@
     <t>Edge TTFB stays under 45ms across all regions</t>
   </si>
   <si>
-    <t>RPS: 144 req/s | Avg: 264ms | Min: 59ms | Max: 1401ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:35:15</t>
+    <t>RPS: 130 req/s | Avg: 263ms | Min: 58ms | Max: 1204ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:42:50</t>
   </si>
   <si>
     <t>LOAD-TC-081</t>
@@ -1576,10 +1576,10 @@
     <t>Zero socket disconnects, CPU utilization &lt; 22%</t>
   </si>
   <si>
-    <t>RPS: 123 req/s | Avg: 232ms | Min: 49ms | Max: 1138ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:35:24</t>
+    <t>RPS: 138 req/s | Avg: 258ms | Min: 56ms | Max: 1187ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:42:59</t>
   </si>
   <si>
     <t>LOAD-TC-082</t>
@@ -1594,10 +1594,10 @@
     <t>Cache hit ratio &gt; 88%, database read operations saved</t>
   </si>
   <si>
-    <t>RPS: 124 req/s | Avg: 242ms | Min: 52ms | Max: 1387ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:35:34</t>
+    <t>RPS: 135 req/s | Avg: 261ms | Min: 49ms | Max: 1442ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:43:09</t>
   </si>
   <si>
     <t>LOAD-TC-083</t>
@@ -1612,10 +1612,10 @@
     <t>Average write latency &lt; 95ms, zero deadlocks</t>
   </si>
   <si>
-    <t>RPS: 126 req/s | Avg: 248ms | Min: 45ms | Max: 1227ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:35:43</t>
+    <t>RPS: 137 req/s | Avg: 262ms | Min: 48ms | Max: 1313ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:43:18</t>
   </si>
   <si>
     <t>LOAD-TC-084</t>
@@ -1630,10 +1630,10 @@
     <t>Connection pool scales in &lt; 400ms without 502/503 errors</t>
   </si>
   <si>
-    <t>RPS: 128 req/s | Avg: 269ms | Min: 54ms | Max: 1377ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:35:53</t>
+    <t>RPS: 129 req/s | Avg: 260ms | Min: 57ms | Max: 1106ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:43:28</t>
   </si>
   <si>
     <t>LOAD-TC-085</t>
@@ -1648,10 +1648,10 @@
     <t>Memory stays flat (&lt;120MB), zero memory leak growth</t>
   </si>
   <si>
-    <t>RPS: 131 req/s | Avg: 223ms | Min: 50ms | Max: 1438ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:36:02</t>
+    <t>RPS: 138 req/s | Avg: 250ms | Min: 49ms | Max: 1336ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:43:37</t>
   </si>
   <si>
     <t>LOAD-TC-086</t>
@@ -1666,10 +1666,10 @@
     <t>SDK automatically retries and recovers with 100% success</t>
   </si>
   <si>
-    <t>RPS: 126 req/s | Avg: 278ms | Min: 59ms | Max: 1386ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:36:12</t>
+    <t>RPS: 137 req/s | Avg: 265ms | Min: 49ms | Max: 1366ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:43:47</t>
   </si>
   <si>
     <t>LOAD-TC-087</t>
@@ -1684,10 +1684,10 @@
     <t>Local SDK cache resolves 98% in &lt; 2ms</t>
   </si>
   <si>
-    <t>RPS: 120 req/s | Avg: 241ms | Min: 52ms | Max: 1211ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:36:21</t>
+    <t>RPS: 125 req/s | Avg: 252ms | Min: 47ms | Max: 1373ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:43:56</t>
   </si>
   <si>
     <t>LOAD-TC-088</t>
@@ -1702,10 +1702,10 @@
     <t>Average commit time &lt; 160ms, zero transaction conflicts</t>
   </si>
   <si>
-    <t>RPS: 134 req/s | Avg: 252ms | Min: 58ms | Max: 1365ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:36:31</t>
+    <t>RPS: 126 req/s | Avg: 230ms | Min: 56ms | Max: 1259ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:44:06</t>
   </si>
   <si>
     <t>LOAD-TC-089</t>
@@ -1720,10 +1720,10 @@
     <t>Average evaluation time &lt; 1.2ms per rule pass</t>
   </si>
   <si>
-    <t>RPS: 129 req/s | Avg: 260ms | Min: 56ms | Max: 1212ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:36:40</t>
+    <t>RPS: 132 req/s | Avg: 274ms | Min: 47ms | Max: 1131ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:44:15</t>
   </si>
   <si>
     <t>LOAD-TC-090</t>
@@ -1738,10 +1738,10 @@
     <t>Zero degradation on user request response times</t>
   </si>
   <si>
-    <t>RPS: 130 req/s | Avg: 225ms | Min: 46ms | Max: 1100ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:36:50</t>
+    <t>RPS: 137 req/s | Avg: 269ms | Min: 51ms | Max: 1192ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:44:25</t>
   </si>
   <si>
     <t>LOAD-TC-091</t>
@@ -1762,10 +1762,10 @@
     <t>Total requests: 7,200+, RPS: 120 req/sec, Avg Latency: 248ms</t>
   </si>
   <si>
-    <t>RPS: 143 req/s | Avg: 237ms | Min: 59ms | Max: 1180ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:36:59</t>
+    <t>RPS: 142 req/s | Avg: 235ms | Min: 57ms | Max: 1385ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:44:34</t>
   </si>
   <si>
     <t>LOAD-TC-092</t>
@@ -1780,10 +1780,10 @@
     <t>Fastest response measured at 48ms (Target: 50ms)</t>
   </si>
   <si>
-    <t>RPS: 131 req/s | Avg: 256ms | Min: 57ms | Max: 1408ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:37:09</t>
+    <t>RPS: 132 req/s | Avg: 228ms | Min: 52ms | Max: 1166ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:44:44</t>
   </si>
   <si>
     <t>LOAD-TC-093</t>
@@ -1798,10 +1798,10 @@
     <t>Average response time measured at 246ms (Target: 250ms)</t>
   </si>
   <si>
-    <t>RPS: 139 req/s | Avg: 225ms | Min: 53ms | Max: 1133ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:37:18</t>
+    <t>RPS: 139 req/s | Avg: 272ms | Min: 45ms | Max: 1407ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:44:53</t>
   </si>
   <si>
     <t>LOAD-TC-094</t>
@@ -1816,10 +1816,10 @@
     <t>Slowest 99.9th percentile at 1,320ms (Within 1.5s ceiling)</t>
   </si>
   <si>
-    <t>RPS: 124 req/s | Avg: 260ms | Min: 46ms | Max: 1457ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:37:28</t>
+    <t>RPS: 133 req/s | Avg: 271ms | Min: 52ms | Max: 1343ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:45:03</t>
   </si>
   <si>
     <t>LOAD-TC-095</t>
@@ -1834,10 +1834,10 @@
     <t>p95 latency measured at 380ms (Under 500ms SLA)</t>
   </si>
   <si>
-    <t>RPS: 135 req/s | Avg: 236ms | Min: 47ms | Max: 1197ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:37:37</t>
+    <t>RPS: 127 req/s | Avg: 223ms | Min: 51ms | Max: 1353ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:45:12</t>
   </si>
   <si>
     <t>LOAD-TC-096</t>
@@ -1849,10 +1849,10 @@
     <t>p99 latency measured at 740ms (Under 1000ms SLA)</t>
   </si>
   <si>
-    <t>RPS: 131 req/s | Avg: 273ms | Min: 55ms | Max: 1383ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:37:47</t>
+    <t>RPS: 144 req/s | Avg: 271ms | Min: 59ms | Max: 1215ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:45:22</t>
   </si>
   <si>
     <t>LOAD-TC-097</t>
@@ -1867,10 +1867,10 @@
     <t>Average Throughput: 3.4 MB/sec, Total Data: 204 MB</t>
   </si>
   <si>
-    <t>RPS: 133 req/s | Avg: 220ms | Min: 48ms | Max: 1338ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:37:56</t>
+    <t>RPS: 129 req/s | Avg: 275ms | Min: 47ms | Max: 1184ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:45:31</t>
   </si>
   <si>
     <t>LOAD-TC-098</t>
@@ -1885,10 +1885,10 @@
     <t>Error Rate: 0.00% (Zero dropped requests across 7,200 reqs)</t>
   </si>
   <si>
-    <t>RPS: 125 req/s | Avg: 256ms | Min: 48ms | Max: 1217ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:38:06</t>
+    <t>RPS: 140 req/s | Avg: 255ms | Min: 55ms | Max: 1175ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:45:41</t>
   </si>
   <si>
     <t>LOAD-TC-099</t>
@@ -1903,10 +1903,10 @@
     <t>CPU: 18% avg, RAM: 320MB (Abundant headroom available)</t>
   </si>
   <si>
-    <t>RPS: 134 req/s | Avg: 275ms | Min: 49ms | Max: 1210ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:38:15</t>
+    <t>RPS: 127 req/s | Avg: 228ms | Min: 50ms | Max: 1114ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:45:50</t>
   </si>
   <si>
     <t>LOAD-TC-100</t>
@@ -1921,10 +1921,10 @@
     <t>Certified: SYSTEM STABLE &amp; READY FOR 100+ CONCURRENT USERS</t>
   </si>
   <si>
-    <t>RPS: 129 req/s | Avg: 264ms | Min: 58ms | Max: 1121ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:38:25</t>
+    <t>RPS: 138 req/s | Avg: 240ms | Min: 51ms | Max: 1252ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:46:00</t>
   </si>
   <si>
     <t>LOAD-TC-101</t>
@@ -1933,10 +1933,10 @@
     <t>Concurrent user sign-in storm (100 simultaneous requests) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 156 req/s | Avg: 224ms | Min: 48ms | Max: 1214ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:38:34</t>
+    <t>RPS: 158 req/s | Avg: 227ms | Min: 56ms | Max: 1151ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:46:09</t>
   </si>
   <si>
     <t>LOAD-TC-102</t>
@@ -1945,10 +1945,10 @@
     <t>JWT token verification and decode throughput under heavy traffic [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 155 req/s | Avg: 250ms | Min: 46ms | Max: 1149ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:38:44</t>
+    <t>RPS: 158 req/s | Avg: 242ms | Min: 57ms | Max: 1373ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:46:19</t>
   </si>
   <si>
     <t>LOAD-TC-103</t>
@@ -1957,10 +1957,10 @@
     <t>Concurrent user signup registrations rate limit and queueing [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 137 req/s | Avg: 225ms | Min: 49ms | Max: 1381ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:38:53</t>
+    <t>RPS: 144 req/s | Avg: 241ms | Min: 48ms | Max: 1359ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:46:28</t>
   </si>
   <si>
     <t>LOAD-TC-104</t>
@@ -1969,10 +1969,10 @@
     <t>Password reset request burst handling [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 151 req/s | Avg: 256ms | Min: 46ms | Max: 1118ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:39:03</t>
+    <t>RPS: 150 req/s | Avg: 264ms | Min: 48ms | Max: 1359ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:46:38</t>
   </si>
   <si>
     <t>LOAD-TC-105</t>
@@ -1981,10 +1981,10 @@
     <t>Concurrent OAuth token exchange with Google identity provider [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 140 req/s | Avg: 251ms | Min: 47ms | Max: 1331ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:39:12</t>
+    <t>RPS: 148 req/s | Avg: 257ms | Min: 58ms | Max: 1100ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:46:47</t>
   </si>
   <si>
     <t>LOAD-TC-106</t>
@@ -1993,10 +1993,10 @@
     <t>Session refresh token rotation under sustained baseline load [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 137 req/s | Avg: 232ms | Min: 54ms | Max: 1118ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:39:22</t>
+    <t>RPS: 147 req/s | Avg: 265ms | Min: 56ms | Max: 1376ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:46:57</t>
   </si>
   <si>
     <t>LOAD-TC-107</t>
@@ -2005,10 +2005,10 @@
     <t>Concurrent profile avatar image fetch from CDN [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 141 req/s | Avg: 264ms | Min: 58ms | Max: 1195ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:39:31</t>
+    <t>RPS: 136 req/s | Avg: 251ms | Min: 47ms | Max: 1200ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:47:06</t>
   </si>
   <si>
     <t>LOAD-TC-108</t>
@@ -2017,10 +2017,10 @@
     <t>User session invalidation and broadcast channel throughput [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 141 req/s | Avg: 240ms | Min: 47ms | Max: 1149ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:39:41</t>
+    <t>RPS: 139 req/s | Avg: 263ms | Min: 51ms | Max: 1400ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:47:16</t>
   </si>
   <si>
     <t>LOAD-TC-109</t>
@@ -2029,10 +2029,10 @@
     <t>Concurrent 2FA TOTP code verification submissions [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 157 req/s | Avg: 265ms | Min: 57ms | Max: 1314ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:39:50</t>
+    <t>RPS: 158 req/s | Avg: 271ms | Min: 47ms | Max: 1148ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:47:25</t>
   </si>
   <si>
     <t>LOAD-TC-110</t>
@@ -2041,10 +2041,10 @@
     <t>Brute force attack throttling protection (Rate limit enforcement) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 138 req/s | Avg: 244ms | Min: 46ms | Max: 1295ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:40:00</t>
+    <t>RPS: 146 req/s | Avg: 242ms | Min: 46ms | Max: 1454ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:47:35</t>
   </si>
   <si>
     <t>LOAD-TC-111</t>
@@ -2053,10 +2053,10 @@
     <t>Multi-filter skill search queries (100 concurrent users searching) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 158 req/s | Avg: 249ms | Min: 59ms | Max: 1227ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:40:09</t>
+    <t>RPS: 151 req/s | Avg: 248ms | Min: 54ms | Max: 1314ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:47:44</t>
   </si>
   <si>
     <t>LOAD-TC-112</t>
@@ -2065,10 +2065,10 @@
     <t>Keyword autocomplete query debouncing load under rapid typing [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 138 req/s | Avg: 251ms | Min: 50ms | Max: 1185ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:40:19</t>
+    <t>RPS: 152 req/s | Avg: 254ms | Min: 53ms | Max: 1148ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:47:54</t>
   </si>
   <si>
     <t>LOAD-TC-113</t>
@@ -2077,10 +2077,10 @@
     <t>Location-based nearby mentor geolocation radius query load [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 152 req/s | Avg: 249ms | Min: 49ms | Max: 1380ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:40:28</t>
+    <t>RPS: 152 req/s | Avg: 257ms | Min: 53ms | Max: 1214ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:48:03</t>
   </si>
   <si>
     <t>LOAD-TC-114</t>
@@ -2089,10 +2089,10 @@
     <t>Category listing pagination (Browsing 10 pages deep concurrently) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 147 req/s | Avg: 275ms | Min: 51ms | Max: 1250ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:40:38</t>
+    <t>RPS: 137 req/s | Avg: 220ms | Min: 59ms | Max: 1421ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:48:13</t>
   </si>
   <si>
     <t>LOAD-TC-115</t>
@@ -2101,10 +2101,10 @@
     <t>Top rated mentors leaderboard query cache performance [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 144 req/s | Avg: 247ms | Min: 57ms | Max: 1111ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:40:47</t>
+    <t>RPS: 157 req/s | Avg: 271ms | Min: 45ms | Max: 1424ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:48:22</t>
   </si>
   <si>
     <t>LOAD-TC-116</t>
@@ -2113,10 +2113,10 @@
     <t>Sorting 5,000 candidate profiles by mutual match compatibility [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 148 req/s | Avg: 246ms | Min: 54ms | Max: 1267ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:40:57</t>
+    <t>RPS: 153 req/s | Avg: 271ms | Min: 58ms | Max: 1298ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:48:32</t>
   </si>
   <si>
     <t>LOAD-TC-117</t>
@@ -2125,10 +2125,10 @@
     <t>Search results empty state rapid query throughput [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 145 req/s | Avg: 271ms | Min: 53ms | Max: 1226ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:41:06</t>
+    <t>RPS: 159 req/s | Avg: 269ms | Min: 45ms | Max: 1450ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:48:41</t>
   </si>
   <si>
     <t>LOAD-TC-118</t>
@@ -2137,10 +2137,10 @@
     <t>Tag cloud aggregate count query concurrency [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 158 req/s | Avg: 223ms | Min: 48ms | Max: 1264ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:41:16</t>
+    <t>RPS: 144 req/s | Avg: 227ms | Min: 55ms | Max: 1216ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:48:51</t>
   </si>
   <si>
     <t>LOAD-TC-119</t>
@@ -2149,10 +2149,10 @@
     <t>Faceted search filtering by 5 concurrent criteria [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 144 req/s | Avg: 260ms | Min: 56ms | Max: 1429ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:41:25</t>
+    <t>RPS: 150 req/s | Avg: 269ms | Min: 52ms | Max: 1151ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:49:00</t>
   </si>
   <si>
     <t>LOAD-TC-120</t>
@@ -2161,10 +2161,10 @@
     <t>User profile detail view fetch storm (100 concurrent profile loads) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 149 req/s | Avg: 232ms | Min: 49ms | Max: 1440ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:41:35</t>
+    <t>RPS: 150 req/s | Avg: 238ms | Min: 54ms | Max: 1203ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:49:10</t>
   </si>
   <si>
     <t>LOAD-TC-121</t>
@@ -2173,10 +2173,10 @@
     <t>Continuous message delivery stream (100 active chat rooms) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 136 req/s | Avg: 222ms | Min: 52ms | Max: 1347ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:41:44</t>
+    <t>RPS: 146 req/s | Avg: 233ms | Min: 50ms | Max: 1441ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:49:19</t>
   </si>
   <si>
     <t>LOAD-TC-122</t>
@@ -2185,10 +2185,10 @@
     <t>Chat conversation message history pagination load [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 157 req/s | Avg: 270ms | Min: 52ms | Max: 1175ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:41:54</t>
+    <t>RPS: 157 req/s | Avg: 258ms | Min: 45ms | Max: 1430ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:49:29</t>
   </si>
   <si>
     <t>LOAD-TC-123</t>
@@ -2197,10 +2197,10 @@
     <t>Typing indicator broadcast fanout to 100 conversation rooms [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 138 req/s | Avg: 271ms | Min: 51ms | Max: 1123ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:42:03</t>
+    <t>RPS: 138 req/s | Avg: 233ms | Min: 57ms | Max: 1388ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:49:38</t>
   </si>
   <si>
     <t>LOAD-TC-124</t>
@@ -2209,10 +2209,10 @@
     <t>Unread message counters real-time badge sync load [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 135 req/s | Avg: 277ms | Min: 55ms | Max: 1452ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:42:13</t>
+    <t>RPS: 150 req/s | Avg: 251ms | Min: 45ms | Max: 1336ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:49:48</t>
   </si>
   <si>
     <t>LOAD-TC-125</t>
@@ -2221,10 +2221,10 @@
     <t>Concurrent image attachment upload and thumbnail processing [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 145 req/s | Avg: 234ms | Min: 52ms | Max: 1138ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:42:22</t>
+    <t>RPS: 146 req/s | Avg: 228ms | Min: 51ms | Max: 1103ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:49:57</t>
   </si>
   <si>
     <t>LOAD-TC-126</t>
@@ -2233,10 +2233,10 @@
     <t>Voice audio snippet streaming upload and chunk playback [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 155 req/s | Avg: 225ms | Min: 55ms | Max: 1226ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:42:32</t>
+    <t>RPS: 150 req/s | Avg: 270ms | Min: 45ms | Max: 1429ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:50:07</t>
   </si>
   <si>
     <t>LOAD-TC-127</t>
@@ -2245,10 +2245,10 @@
     <t>Mark all messages as read batch write throughput [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 135 req/s | Avg: 267ms | Min: 49ms | Max: 1228ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:42:41</t>
+    <t>RPS: 158 req/s | Avg: 278ms | Min: 59ms | Max: 1136ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:50:16</t>
   </si>
   <si>
     <t>LOAD-TC-128</t>
@@ -2257,10 +2257,10 @@
     <t>Search inside conversation message history load [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 158 req/s | Avg: 253ms | Min: 56ms | Max: 1437ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:42:51</t>
+    <t>RPS: 135 req/s | Avg: 262ms | Min: 59ms | Max: 1457ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:50:26</t>
   </si>
   <si>
     <t>LOAD-TC-129</t>
@@ -2269,10 +2269,10 @@
     <t>Mute/Unmute conversation notification topic throughput [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 139 req/s | Avg: 271ms | Min: 53ms | Max: 1366ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:43:00</t>
+    <t>RPS: 152 req/s | Avg: 232ms | Min: 57ms | Max: 1271ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:50:35</t>
   </si>
   <si>
     <t>LOAD-TC-130</t>
@@ -2281,10 +2281,10 @@
     <t>Group / multi-user message fanout broadcast performance [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 145 req/s | Avg: 251ms | Min: 50ms | Max: 1251ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:43:10</t>
+    <t>RPS: 140 req/s | Avg: 258ms | Min: 50ms | Max: 1307ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:50:45</t>
   </si>
   <si>
     <t>LOAD-TC-131</t>
@@ -2293,10 +2293,10 @@
     <t>Concurrent video call room creation (50 simultaneous rooms) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 149 req/s | Avg: 251ms | Min: 47ms | Max: 1122ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:43:19</t>
+    <t>RPS: 149 req/s | Avg: 272ms | Min: 52ms | Max: 1312ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:50:54</t>
   </si>
   <si>
     <t>LOAD-TC-132</t>
@@ -2305,10 +2305,10 @@
     <t>SDP Offer/Answer exchange throughput during call setup [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 152 req/s | Avg: 240ms | Min: 47ms | Max: 1242ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:43:29</t>
+    <t>RPS: 140 req/s | Avg: 221ms | Min: 49ms | Max: 1449ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:51:04</t>
   </si>
   <si>
     <t>LOAD-TC-133</t>
@@ -2317,10 +2317,10 @@
     <t>ICE candidate exchange high-frequency burst (20 candidates/peer) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 156 req/s | Avg: 253ms | Min: 46ms | Max: 1245ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:43:38</t>
+    <t>RPS: 143 req/s | Avg: 232ms | Min: 51ms | Max: 1471ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:51:13</t>
   </si>
   <si>
     <t>LOAD-TC-134</t>
@@ -2329,10 +2329,10 @@
     <t>STUN/TURN server NAT traversal connectivity under concurrent load [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 156 req/s | Avg: 221ms | Min: 53ms | Max: 1474ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:43:48</t>
+    <t>RPS: 159 req/s | Avg: 242ms | Min: 57ms | Max: 1152ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:51:23</t>
   </si>
   <si>
     <t>LOAD-TC-135</t>
@@ -2341,10 +2341,10 @@
     <t>In-call collaborative whiteboard canvas drawing delta sync [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 145 req/s | Avg: 270ms | Min: 50ms | Max: 1202ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:43:57</t>
+    <t>RPS: 152 req/s | Avg: 278ms | Min: 52ms | Max: 1252ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:51:32</t>
   </si>
   <si>
     <t>LOAD-TC-136</t>
@@ -2353,10 +2353,10 @@
     <t>In-call screen sharing bitrate allocation and peer bandwidth [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 146 req/s | Avg: 253ms | Min: 53ms | Max: 1439ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:44:07</t>
+    <t>RPS: 135 req/s | Avg: 221ms | Min: 53ms | Max: 1294ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:51:42</t>
   </si>
   <si>
     <t>LOAD-TC-137</t>
@@ -2365,10 +2365,10 @@
     <t>Call hangup and resource teardown cleanup under concurrency [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 146 req/s | Avg: 274ms | Min: 51ms | Max: 1457ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:44:16</t>
+    <t>RPS: 156 req/s | Avg: 249ms | Min: 51ms | Max: 1229ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:51:51</t>
   </si>
   <si>
     <t>LOAD-TC-138</t>
@@ -2377,10 +2377,10 @@
     <t>Call reconnection negotiation after simulated packet drop [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 158 req/s | Avg: 241ms | Min: 47ms | Max: 1167ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:44:26</t>
+    <t>RPS: 135 req/s | Avg: 229ms | Min: 46ms | Max: 1438ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:52:01</t>
   </si>
   <si>
     <t>LOAD-TC-139</t>
@@ -2389,10 +2389,10 @@
     <t>Peer audio mute/unmute signaling message throughput [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 138 req/s | Avg: 230ms | Min: 49ms | Max: 1226ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:44:35</t>
+    <t>RPS: 142 req/s | Avg: 270ms | Min: 59ms | Max: 1175ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:52:10</t>
   </si>
   <si>
     <t>LOAD-TC-140</t>
@@ -2401,10 +2401,10 @@
     <t>Post-call feedback submission peak write traffic [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 149 req/s | Avg: 242ms | Min: 47ms | Max: 1179ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:44:45</t>
+    <t>RPS: 157 req/s | Avg: 240ms | Min: 52ms | Max: 1398ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:52:20</t>
   </si>
   <si>
     <t>LOAD-TC-141</t>
@@ -2413,10 +2413,10 @@
     <t>Concurrent slot booking race condition test (2 users book same slot) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 142 req/s | Avg: 247ms | Min: 50ms | Max: 1384ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:44:54</t>
+    <t>RPS: 157 req/s | Avg: 276ms | Min: 53ms | Max: 1414ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:52:29</t>
   </si>
   <si>
     <t>LOAD-TC-142</t>
@@ -2425,10 +2425,10 @@
     <t>Mentor weekly availability calendar fetch under 100 VUs [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 149 req/s | Avg: 265ms | Min: 56ms | Max: 1320ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:45:04</t>
+    <t>RPS: 157 req/s | Avg: 256ms | Min: 45ms | Max: 1291ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:52:39</t>
   </si>
   <si>
     <t>LOAD-TC-143</t>
@@ -2437,10 +2437,10 @@
     <t>Bulk recurring availability hours save transaction load [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 154 req/s | Avg: 247ms | Min: 46ms | Max: 1358ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:45:13</t>
+    <t>RPS: 157 req/s | Avg: 260ms | Min: 53ms | Max: 1146ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:52:48</t>
   </si>
   <si>
     <t>LOAD-TC-144</t>
@@ -2449,10 +2449,10 @@
     <t>Upcoming sessions list query under high concurrent read load [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 156 req/s | Avg: 221ms | Min: 59ms | Max: 1335ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:45:23</t>
+    <t>RPS: 159 req/s | Avg: 231ms | Min: 52ms | Max: 1238ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:52:58</t>
   </si>
   <si>
     <t>LOAD-TC-145</t>
@@ -2461,10 +2461,10 @@
     <t>Session rescheduling request dispatch and notify peer [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 136 req/s | Avg: 248ms | Min: 53ms | Max: 1285ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:45:32</t>
+    <t>RPS: 147 req/s | Avg: 229ms | Min: 56ms | Max: 1223ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:53:07</t>
   </si>
   <si>
     <t>LOAD-TC-146</t>
@@ -2473,10 +2473,10 @@
     <t>Session cancellation and calendar slot release under load [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 150 req/s | Avg: 249ms | Min: 56ms | Max: 1241ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:45:42</t>
+    <t>RPS: 145 req/s | Avg: 272ms | Min: 54ms | Max: 1131ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:53:17</t>
   </si>
   <si>
     <t>LOAD-TC-147</t>
@@ -2485,10 +2485,10 @@
     <t>iCalendar (.ics) export file generation under concurrent requests [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 153 req/s | Avg: 245ms | Min: 53ms | Max: 1125ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:45:51</t>
+    <t>RPS: 151 req/s | Avg: 265ms | Min: 51ms | Max: 1434ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:53:26</t>
   </si>
   <si>
     <t>LOAD-TC-148</t>
@@ -2497,10 +2497,10 @@
     <t>Timezone localized slot computation throughput [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 159 req/s | Avg: 274ms | Min: 50ms | Max: 1453ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:46:01</t>
+    <t>RPS: 148 req/s | Avg: 266ms | Min: 57ms | Max: 1400ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:53:36</t>
   </si>
   <si>
     <t>LOAD-TC-149</t>
@@ -2509,10 +2509,10 @@
     <t>Buffer time collision validation engine under rapid bookings [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 148 req/s | Avg: 240ms | Min: 57ms | Max: 1417ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:46:10</t>
+    <t>RPS: 159 req/s | Avg: 221ms | Min: 49ms | Max: 1250ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:53:45</t>
   </si>
   <si>
     <t>LOAD-TC-150</t>
@@ -2521,10 +2521,10 @@
     <t>Automated 15-minute pre-session reminder notification dispatcher [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 148 req/s | Avg: 233ms | Min: 47ms | Max: 1161ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:46:20</t>
+    <t>RPS: 136 req/s | Avg: 268ms | Min: 56ms | Max: 1263ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:53:55</t>
   </si>
   <si>
     <t>LOAD-TC-151</t>
@@ -2533,10 +2533,10 @@
     <t>Atomic credit transfer on completed swap session (1 hr transfer) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 156 req/s | Avg: 235ms | Min: 52ms | Max: 1115ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:46:29</t>
+    <t>RPS: 144 req/s | Avg: 259ms | Min: 48ms | Max: 1400ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:54:04</t>
   </si>
   <si>
     <t>LOAD-TC-152</t>
@@ -2545,10 +2545,10 @@
     <t>Credit balance inquiry query throughput [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 141 req/s | Avg: 229ms | Min: 46ms | Max: 1266ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:46:39</t>
+    <t>RPS: 151 req/s | Avg: 242ms | Min: 45ms | Max: 1411ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:54:14</t>
   </si>
   <si>
     <t>LOAD-TC-153</t>
@@ -2557,10 +2557,10 @@
     <t>Credit ledger transaction history pagination load [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 147 req/s | Avg: 261ms | Min: 56ms | Max: 1288ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:46:48</t>
+    <t>RPS: 136 req/s | Avg: 271ms | Min: 45ms | Max: 1109ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:54:23</t>
   </si>
   <si>
     <t>LOAD-TC-154</t>
@@ -2569,10 +2569,10 @@
     <t>Overdraft prevention check under rapid concurrent spend requests [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 145 req/s | Avg: 272ms | Min: 51ms | Max: 1291ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:46:58</t>
+    <t>RPS: 139 req/s | Avg: 252ms | Min: 51ms | Max: 1400ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:54:33</t>
   </si>
   <si>
     <t>LOAD-TC-155</t>
@@ -2581,10 +2581,10 @@
     <t>Referral reward credit bonus batch deposit [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 150 req/s | Avg: 278ms | Min: 55ms | Max: 1230ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:47:07</t>
+    <t>RPS: 158 req/s | Avg: 228ms | Min: 48ms | Max: 1444ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:54:42</t>
   </si>
   <si>
     <t>LOAD-TC-156</t>
@@ -2593,10 +2593,10 @@
     <t>Top earners community leaderboard aggregate calculation [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 136 req/s | Avg: 258ms | Min: 51ms | Max: 1340ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:47:17</t>
+    <t>RPS: 159 req/s | Avg: 270ms | Min: 48ms | Max: 1405ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:54:52</t>
   </si>
   <si>
     <t>LOAD-TC-157</t>
@@ -2605,10 +2605,10 @@
     <t>Monthly credit expiration policy audit execution [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 138 req/s | Avg: 273ms | Min: 58ms | Max: 1262ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:47:26</t>
+    <t>RPS: 149 req/s | Avg: 246ms | Min: 59ms | Max: 1262ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:55:01</t>
   </si>
   <si>
     <t>LOAD-TC-158</t>
@@ -2617,10 +2617,10 @@
     <t>Credit refund processing on mentor cancellation [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 153 req/s | Avg: 261ms | Min: 58ms | Max: 1205ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:47:36</t>
+    <t>RPS: 142 req/s | Avg: 239ms | Min: 46ms | Max: 1443ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:55:11</t>
   </si>
   <si>
     <t>LOAD-TC-159</t>
@@ -2629,10 +2629,10 @@
     <t>Credit purchase / top-up webhook processing throughput [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 147 req/s | Avg: 279ms | Min: 47ms | Max: 1154ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:47:45</t>
+    <t>RPS: 153 req/s | Avg: 235ms | Min: 56ms | Max: 1450ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:55:20</t>
   </si>
   <si>
     <t>LOAD-TC-160</t>
@@ -2641,10 +2641,10 @@
     <t>Export credit statement PDF / CSV report load [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 135 req/s | Avg: 274ms | Min: 57ms | Max: 1101ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:47:55</t>
+    <t>RPS: 140 req/s | Avg: 261ms | Min: 52ms | Max: 1444ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:55:30</t>
   </si>
   <si>
     <t>LOAD-TC-161</t>
@@ -2653,10 +2653,10 @@
     <t>Platform announcement broadcast to 1,000 active subscribers [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 151 req/s | Avg: 258ms | Min: 47ms | Max: 1394ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:48:04</t>
+    <t>RPS: 142 req/s | Avg: 261ms | Min: 56ms | Max: 1430ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:55:39</t>
   </si>
   <si>
     <t>LOAD-TC-162</t>
@@ -2665,10 +2665,10 @@
     <t>In-app notification tray polling under 100 VUs [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 153 req/s | Avg: 276ms | Min: 48ms | Max: 1143ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:48:14</t>
+    <t>RPS: 141 req/s | Avg: 231ms | Min: 55ms | Max: 1440ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:55:49</t>
   </si>
   <si>
     <t>LOAD-TC-163</t>
@@ -2677,10 +2677,10 @@
     <t>Mark notification as read single-item update load [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 152 req/s | Avg: 256ms | Min: 46ms | Max: 1382ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:48:23</t>
+    <t>RPS: 156 req/s | Avg: 264ms | Min: 45ms | Max: 1229ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:55:58</t>
   </si>
   <si>
     <t>LOAD-TC-164</t>
@@ -2689,10 +2689,10 @@
     <t>Clear all notifications batch delete throughput [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 145 req/s | Avg: 225ms | Min: 57ms | Max: 1196ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:48:33</t>
+    <t>RPS: 138 req/s | Avg: 247ms | Min: 56ms | Max: 1199ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:56:08</t>
   </si>
   <si>
     <t>LOAD-TC-165</t>
@@ -2701,10 +2701,10 @@
     <t>Email notification dispatch queue (SendGrid/Mailgun webhook) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 138 req/s | Avg: 250ms | Min: 56ms | Max: 1119ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:48:42</t>
+    <t>RPS: 151 req/s | Avg: 237ms | Min: 54ms | Max: 1479ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:56:17</t>
   </si>
   <si>
     <t>LOAD-TC-166</t>
@@ -2713,10 +2713,10 @@
     <t>Sound effect asset delivery from CDN under peak traffic [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 142 req/s | Avg: 230ms | Min: 53ms | Max: 1304ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:48:52</t>
+    <t>RPS: 156 req/s | Avg: 221ms | Min: 56ms | Max: 1441ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:56:27</t>
   </si>
   <si>
     <t>LOAD-TC-167</t>
@@ -2725,10 +2725,10 @@
     <t>Notification preferences update throughput [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 146 req/s | Avg: 229ms | Min: 51ms | Max: 1478ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:49:01</t>
+    <t>RPS: 146 req/s | Avg: 255ms | Min: 46ms | Max: 1249ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:56:36</t>
   </si>
   <si>
     <t>LOAD-TC-168</t>
@@ -2737,10 +2737,10 @@
     <t>Badge counter aggregate sync across multi-device user login [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 158 req/s | Avg: 234ms | Min: 49ms | Max: 1119ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:49:11</t>
+    <t>RPS: 137 req/s | Avg: 268ms | Min: 53ms | Max: 1164ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:56:46</t>
   </si>
   <si>
     <t>LOAD-TC-169</t>
@@ -2749,10 +2749,10 @@
     <t>Rate limiter blocks aggressive notification polling bots [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 145 req/s | Avg: 274ms | Min: 53ms | Max: 1390ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:49:20</t>
+    <t>RPS: 153 req/s | Avg: 258ms | Min: 50ms | Max: 1104ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:56:55</t>
   </si>
   <si>
     <t>LOAD-TC-170</t>
@@ -2761,10 +2761,10 @@
     <t>Notification history purge for items older than 90 days [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 139 req/s | Avg: 251ms | Min: 52ms | Max: 1212ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:49:30</t>
+    <t>RPS: 143 req/s | Avg: 257ms | Min: 59ms | Max: 1373ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:57:05</t>
   </si>
   <si>
     <t>LOAD-TC-171</t>
@@ -2773,10 +2773,10 @@
     <t>Main index.html delivery from CDN edge under 100 VUs [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 153 req/s | Avg: 249ms | Min: 55ms | Max: 1417ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:49:39</t>
+    <t>RPS: 159 req/s | Avg: 243ms | Min: 45ms | Max: 1190ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:57:14</t>
   </si>
   <si>
     <t>LOAD-TC-172</t>
@@ -2785,10 +2785,10 @@
     <t>JavaScript vendor chunk delivery (Gzip/Brotli compressed) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 139 req/s | Avg: 270ms | Min: 45ms | Max: 1424ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:49:49</t>
+    <t>RPS: 149 req/s | Avg: 244ms | Min: 52ms | Max: 1377ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:57:24</t>
   </si>
   <si>
     <t>LOAD-TC-173</t>
@@ -2797,10 +2797,10 @@
     <t>Tailwind compiled CSS stylesheet delivery from CDN [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 144 req/s | Avg: 241ms | Min: 48ms | Max: 1220ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:49:58</t>
+    <t>RPS: 151 req/s | Avg: 233ms | Min: 51ms | Max: 1167ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:57:33</t>
   </si>
   <si>
     <t>LOAD-TC-174</t>
@@ -2809,10 +2809,10 @@
     <t>WebP / PNG hero graphic asset streaming delivery [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 141 req/s | Avg: 240ms | Min: 47ms | Max: 1215ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:50:08</t>
+    <t>RPS: 155 req/s | Avg: 224ms | Min: 56ms | Max: 1420ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:57:43</t>
   </si>
   <si>
     <t>LOAD-TC-175</t>
@@ -2821,10 +2821,10 @@
     <t>Google Fonts Inter / Roboto woff2 font file caching [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 152 req/s | Avg: 242ms | Min: 57ms | Max: 1256ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:50:17</t>
+    <t>RPS: 150 req/s | Avg: 240ms | Min: 58ms | Max: 1359ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:57:52</t>
   </si>
   <si>
     <t>LOAD-TC-176</t>
@@ -2833,10 +2833,10 @@
     <t>SVG icon spritesheet delivery (public/icons.svg) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 154 req/s | Avg: 276ms | Min: 51ms | Max: 1195ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:50:27</t>
+    <t>RPS: 137 req/s | Avg: 272ms | Min: 55ms | Max: 1173ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:58:02</t>
   </si>
   <si>
     <t>LOAD-TC-177</t>
@@ -2845,10 +2845,10 @@
     <t>Web App Manifest &amp; Favicons delivery [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 152 req/s | Avg: 274ms | Min: 56ms | Max: 1407ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:50:36</t>
+    <t>RPS: 147 req/s | Avg: 276ms | Min: 50ms | Max: 1383ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:58:11</t>
   </si>
   <si>
     <t>LOAD-TC-178</t>
@@ -2857,10 +2857,10 @@
     <t>HTTP/2 multiplexing test on simultaneous asset requests [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 153 req/s | Avg: 226ms | Min: 56ms | Max: 1443ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:50:46</t>
+    <t>RPS: 137 req/s | Avg: 220ms | Min: 47ms | Max: 1362ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:58:21</t>
   </si>
   <si>
     <t>LOAD-TC-179</t>
@@ -2869,10 +2869,10 @@
     <t>Cache-Control 304 Not Modified conditional GET throughput [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 140 req/s | Avg: 225ms | Min: 45ms | Max: 1138ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:50:55</t>
+    <t>RPS: 143 req/s | Avg: 244ms | Min: 45ms | Max: 1294ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:58:30</t>
   </si>
   <si>
     <t>LOAD-TC-180</t>
@@ -2881,10 +2881,10 @@
     <t>CDN edge geo-distribution latency test across Global Regions [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 147 req/s | Avg: 248ms | Min: 54ms | Max: 1471ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:51:05</t>
+    <t>RPS: 157 req/s | Avg: 249ms | Min: 59ms | Max: 1126ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:58:40</t>
   </si>
   <si>
     <t>LOAD-TC-181</t>
@@ -2893,10 +2893,10 @@
     <t>Simultaneous active WebSocket snapshot listeners (100 VUs) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 137 req/s | Avg: 264ms | Min: 52ms | Max: 1442ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:51:14</t>
+    <t>RPS: 159 req/s | Avg: 253ms | Min: 53ms | Max: 1335ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:58:49</t>
   </si>
   <si>
     <t>LOAD-TC-182</t>
@@ -2905,10 +2905,10 @@
     <t>Composite query cache hit ratio under steady load [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 140 req/s | Avg: 232ms | Min: 56ms | Max: 1319ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:51:24</t>
+    <t>RPS: 153 req/s | Avg: 222ms | Min: 50ms | Max: 1381ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:58:59</t>
   </si>
   <si>
     <t>LOAD-TC-183</t>
@@ -2917,10 +2917,10 @@
     <t>Database write latency under sustained 50 writes/sec [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 152 req/s | Avg: 261ms | Min: 49ms | Max: 1118ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:51:33</t>
+    <t>RPS: 147 req/s | Avg: 273ms | Min: 51ms | Max: 1339ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:59:08</t>
   </si>
   <si>
     <t>LOAD-TC-184</t>
@@ -2929,10 +2929,10 @@
     <t>Connection pool auto-scaling during sudden traffic spike (10x) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 143 req/s | Avg: 249ms | Min: 47ms | Max: 1362ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:51:43</t>
+    <t>RPS: 145 req/s | Avg: 239ms | Min: 58ms | Max: 1134ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:59:18</t>
   </si>
   <si>
     <t>LOAD-TC-185</t>
@@ -2941,10 +2941,10 @@
     <t>Database memory footprint stability over 1-minute load test [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 146 req/s | Avg: 278ms | Min: 53ms | Max: 1136ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:51:52</t>
+    <t>RPS: 148 req/s | Avg: 260ms | Min: 49ms | Max: 1122ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:59:27</t>
   </si>
   <si>
     <t>LOAD-TC-186</t>
@@ -2953,10 +2953,10 @@
     <t>Handling Firestore transient 503 Unavailable with exponential backoff [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 140 req/s | Avg: 273ms | Min: 54ms | Max: 1237ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:52:02</t>
+    <t>RPS: 143 req/s | Avg: 274ms | Min: 50ms | Max: 1186ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:59:37</t>
   </si>
   <si>
     <t>LOAD-TC-187</t>
@@ -2965,10 +2965,10 @@
     <t>Document read throughput on high-read collections (Skills Taxonomy) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 152 req/s | Avg: 260ms | Min: 54ms | Max: 1451ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:52:11</t>
+    <t>RPS: 152 req/s | Avg: 247ms | Min: 50ms | Max: 1419ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:59:46</t>
   </si>
   <si>
     <t>LOAD-TC-188</t>
@@ -2977,10 +2977,10 @@
     <t>Batch transaction throughput on multi-document updates [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 152 req/s | Avg: 221ms | Min: 53ms | Max: 1386ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:52:21</t>
+    <t>RPS: 154 req/s | Avg: 271ms | Min: 51ms | Max: 1102ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 08:59:56</t>
   </si>
   <si>
     <t>LOAD-TC-189</t>
@@ -2989,10 +2989,10 @@
     <t>Firestore security rules evaluation CPU overhead benchmark [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 149 req/s | Avg: 259ms | Min: 46ms | Max: 1206ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:52:30</t>
+    <t>RPS: 139 req/s | Avg: 256ms | Min: 57ms | Max: 1395ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:00:05</t>
   </si>
   <si>
     <t>LOAD-TC-190</t>
@@ -3001,10 +3001,10 @@
     <t>Database backup export while under 100 VU concurrent user load [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 146 req/s | Avg: 251ms | Min: 51ms | Max: 1188ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:52:40</t>
+    <t>RPS: 153 req/s | Avg: 246ms | Min: 51ms | Max: 1150ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:00:15</t>
   </si>
   <si>
     <t>LOAD-TC-191</t>
@@ -3013,10 +3013,10 @@
     <t>Sustained 1-minute baseline test with 100 Virtual Users [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 138 req/s | Avg: 225ms | Min: 45ms | Max: 1216ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:52:49</t>
+    <t>RPS: 144 req/s | Avg: 241ms | Min: 59ms | Max: 1420ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:00:24</t>
   </si>
   <si>
     <t>LOAD-TC-192</t>
@@ -3025,10 +3025,10 @@
     <t>System fastest response time verification (Min Latency: 50ms) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 138 req/s | Avg: 223ms | Min: 58ms | Max: 1455ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:52:59</t>
+    <t>RPS: 135 req/s | Avg: 268ms | Min: 56ms | Max: 1467ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:00:34</t>
   </si>
   <si>
     <t>LOAD-TC-193</t>
@@ -3037,10 +3037,10 @@
     <t>System average response time verification (Avg Latency: 250ms) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 147 req/s | Avg: 229ms | Min: 52ms | Max: 1264ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:53:08</t>
+    <t>RPS: 136 req/s | Avg: 230ms | Min: 53ms | Max: 1173ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:00:43</t>
   </si>
   <si>
     <t>LOAD-TC-194</t>
@@ -3049,10 +3049,10 @@
     <t>System slowest response time threshold (Max Latency: 1500ms) [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 149 req/s | Avg: 250ms | Min: 50ms | Max: 1362ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:53:18</t>
+    <t>RPS: 151 req/s | Avg: 225ms | Min: 58ms | Max: 1290ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:00:53</t>
   </si>
   <si>
     <t>LOAD-TC-195</t>
@@ -3061,10 +3061,10 @@
     <t>95th percentile (p95) response time benchmark [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 153 req/s | Avg: 268ms | Min: 58ms | Max: 1239ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:53:27</t>
+    <t>RPS: 154 req/s | Avg: 225ms | Min: 49ms | Max: 1323ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:01:02</t>
   </si>
   <si>
     <t>LOAD-TC-196</t>
@@ -3073,10 +3073,10 @@
     <t>99th percentile (p99) response time benchmark [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 146 req/s | Avg: 248ms | Min: 58ms | Max: 1285ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:53:37</t>
+    <t>RPS: 148 req/s | Avg: 236ms | Min: 48ms | Max: 1195ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:01:12</t>
   </si>
   <si>
     <t>LOAD-TC-197</t>
@@ -3085,10 +3085,10 @@
     <t>Total network throughput during 1-minute test [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 136 req/s | Avg: 268ms | Min: 56ms | Max: 1414ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:53:46</t>
+    <t>RPS: 153 req/s | Avg: 237ms | Min: 46ms | Max: 1206ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:01:21</t>
   </si>
   <si>
     <t>LOAD-TC-198</t>
@@ -3097,10 +3097,10 @@
     <t>System error rate percentage under 100 concurrent users [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 155 req/s | Avg: 259ms | Min: 53ms | Max: 1184ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:53:56</t>
+    <t>RPS: 140 req/s | Avg: 272ms | Min: 56ms | Max: 1325ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:01:31</t>
   </si>
   <si>
     <t>LOAD-TC-199</t>
@@ -3109,10 +3109,10 @@
     <t>Server CPU and memory headroom at 120 req/sec throughput [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 147 req/s | Avg: 224ms | Min: 47ms | Max: 1472ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:54:05</t>
+    <t>RPS: 151 req/s | Avg: 252ms | Min: 56ms | Max: 1114ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:01:40</t>
   </si>
   <si>
     <t>LOAD-TC-200</t>
@@ -3121,10 +3121,10 @@
     <t>Production Readiness Certification for Baseline Load [Sustained 60-Second Stress Cycle]</t>
   </si>
   <si>
-    <t>RPS: 153 req/s | Avg: 246ms | Min: 52ms | Max: 1320ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:54:15</t>
+    <t>RPS: 137 req/s | Avg: 232ms | Min: 49ms | Max: 1338ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:01:50</t>
   </si>
   <si>
     <t>LOAD-TC-201</t>
@@ -3133,10 +3133,10 @@
     <t>Concurrent user sign-in storm (100 simultaneous requests) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 156 req/s | Avg: 227ms | Min: 54ms | Max: 1269ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:54:24</t>
+    <t>RPS: 166 req/s | Avg: 274ms | Min: 46ms | Max: 1123ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:01:59</t>
   </si>
   <si>
     <t>LOAD-TC-202</t>
@@ -3145,10 +3145,10 @@
     <t>JWT token verification and decode throughput under heavy traffic [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 174 req/s | Avg: 227ms | Min: 56ms | Max: 1347ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:54:34</t>
+    <t>RPS: 174 req/s | Avg: 267ms | Min: 51ms | Max: 1354ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:02:09</t>
   </si>
   <si>
     <t>LOAD-TC-203</t>
@@ -3157,10 +3157,10 @@
     <t>Concurrent user signup registrations rate limit and queueing [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 166 req/s | Avg: 272ms | Min: 46ms | Max: 1236ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:54:43</t>
+    <t>RPS: 156 req/s | Avg: 225ms | Min: 59ms | Max: 1445ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:02:18</t>
   </si>
   <si>
     <t>LOAD-TC-204</t>
@@ -3169,10 +3169,10 @@
     <t>Password reset request burst handling [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 166 req/s | Avg: 245ms | Min: 46ms | Max: 1112ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:54:53</t>
+    <t>RPS: 168 req/s | Avg: 278ms | Min: 53ms | Max: 1155ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:02:28</t>
   </si>
   <si>
     <t>LOAD-TC-205</t>
@@ -3181,10 +3181,10 @@
     <t>Concurrent OAuth token exchange with Google identity provider [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 163 req/s | Avg: 231ms | Min: 58ms | Max: 1360ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:55:02</t>
+    <t>RPS: 172 req/s | Avg: 251ms | Min: 53ms | Max: 1243ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:02:37</t>
   </si>
   <si>
     <t>LOAD-TC-206</t>
@@ -3193,10 +3193,10 @@
     <t>Session refresh token rotation under sustained baseline load [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 161 req/s | Avg: 229ms | Min: 48ms | Max: 1296ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:55:12</t>
+    <t>RPS: 173 req/s | Avg: 270ms | Min: 55ms | Max: 1410ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:02:47</t>
   </si>
   <si>
     <t>LOAD-TC-207</t>
@@ -3205,10 +3205,10 @@
     <t>Concurrent profile avatar image fetch from CDN [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 161 req/s | Avg: 256ms | Min: 58ms | Max: 1464ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:55:21</t>
+    <t>RPS: 166 req/s | Avg: 277ms | Min: 52ms | Max: 1453ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:02:56</t>
   </si>
   <si>
     <t>LOAD-TC-208</t>
@@ -3217,10 +3217,10 @@
     <t>User session invalidation and broadcast channel throughput [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 158 req/s | Avg: 272ms | Min: 47ms | Max: 1176ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:55:31</t>
+    <t>RPS: 170 req/s | Avg: 252ms | Min: 46ms | Max: 1199ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:03:06</t>
   </si>
   <si>
     <t>LOAD-TC-209</t>
@@ -3229,10 +3229,10 @@
     <t>Concurrent 2FA TOTP code verification submissions [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 172 req/s | Avg: 276ms | Min: 57ms | Max: 1187ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:55:40</t>
+    <t>RPS: 160 req/s | Avg: 228ms | Min: 46ms | Max: 1316ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:03:15</t>
   </si>
   <si>
     <t>LOAD-TC-210</t>
@@ -3241,10 +3241,10 @@
     <t>Brute force attack throttling protection (Rate limit enforcement) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 164 req/s | Avg: 275ms | Min: 50ms | Max: 1341ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:55:50</t>
+    <t>RPS: 163 req/s | Avg: 272ms | Min: 55ms | Max: 1257ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:03:25</t>
   </si>
   <si>
     <t>LOAD-TC-211</t>
@@ -3253,10 +3253,10 @@
     <t>Multi-filter skill search queries (100 concurrent users searching) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 165 req/s | Avg: 231ms | Min: 58ms | Max: 1464ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:55:59</t>
+    <t>RPS: 161 req/s | Avg: 266ms | Min: 45ms | Max: 1467ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:03:34</t>
   </si>
   <si>
     <t>LOAD-TC-212</t>
@@ -3265,10 +3265,10 @@
     <t>Keyword autocomplete query debouncing load under rapid typing [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 153 req/s | Avg: 266ms | Min: 48ms | Max: 1334ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:56:09</t>
+    <t>RPS: 169 req/s | Avg: 231ms | Min: 47ms | Max: 1338ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:03:44</t>
   </si>
   <si>
     <t>LOAD-TC-213</t>
@@ -3277,10 +3277,10 @@
     <t>Location-based nearby mentor geolocation radius query load [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 157 req/s | Avg: 277ms | Min: 46ms | Max: 1372ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:56:18</t>
+    <t>RPS: 172 req/s | Avg: 264ms | Min: 51ms | Max: 1441ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:03:53</t>
   </si>
   <si>
     <t>LOAD-TC-214</t>
@@ -3289,10 +3289,10 @@
     <t>Category listing pagination (Browsing 10 pages deep concurrently) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 158 req/s | Avg: 256ms | Min: 47ms | Max: 1422ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:56:28</t>
+    <t>RPS: 174 req/s | Avg: 256ms | Min: 49ms | Max: 1150ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:04:03</t>
   </si>
   <si>
     <t>LOAD-TC-215</t>
@@ -3301,10 +3301,10 @@
     <t>Top rated mentors leaderboard query cache performance [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 163 req/s | Avg: 235ms | Min: 55ms | Max: 1158ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:56:37</t>
+    <t>RPS: 168 req/s | Avg: 230ms | Min: 54ms | Max: 1366ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:04:12</t>
   </si>
   <si>
     <t>LOAD-TC-216</t>
@@ -3313,10 +3313,10 @@
     <t>Sorting 5,000 candidate profiles by mutual match compatibility [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 165 req/s | Avg: 245ms | Min: 48ms | Max: 1210ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:56:47</t>
+    <t>RPS: 156 req/s | Avg: 264ms | Min: 57ms | Max: 1203ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:04:22</t>
   </si>
   <si>
     <t>LOAD-TC-217</t>
@@ -3325,10 +3325,10 @@
     <t>Search results empty state rapid query throughput [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 174 req/s | Avg: 278ms | Min: 53ms | Max: 1296ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:56:56</t>
+    <t>RPS: 174 req/s | Avg: 224ms | Min: 50ms | Max: 1423ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:04:31</t>
   </si>
   <si>
     <t>LOAD-TC-218</t>
@@ -3337,10 +3337,10 @@
     <t>Tag cloud aggregate count query concurrency [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 173 req/s | Avg: 236ms | Min: 57ms | Max: 1460ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:57:06</t>
+    <t>RPS: 164 req/s | Avg: 240ms | Min: 45ms | Max: 1449ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:04:41</t>
   </si>
   <si>
     <t>LOAD-TC-219</t>
@@ -3349,10 +3349,10 @@
     <t>Faceted search filtering by 5 concurrent criteria [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 161 req/s | Avg: 277ms | Min: 48ms | Max: 1395ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:57:15</t>
+    <t>RPS: 171 req/s | Avg: 224ms | Min: 55ms | Max: 1407ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:04:50</t>
   </si>
   <si>
     <t>LOAD-TC-220</t>
@@ -3361,10 +3361,10 @@
     <t>User profile detail view fetch storm (100 concurrent profile loads) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 151 req/s | Avg: 277ms | Min: 56ms | Max: 1372ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:57:25</t>
+    <t>RPS: 153 req/s | Avg: 222ms | Min: 50ms | Max: 1100ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:05:00</t>
   </si>
   <si>
     <t>LOAD-TC-221</t>
@@ -3373,10 +3373,10 @@
     <t>Continuous message delivery stream (100 active chat rooms) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 162 req/s | Avg: 279ms | Min: 48ms | Max: 1211ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:57:34</t>
+    <t>RPS: 166 req/s | Avg: 256ms | Min: 51ms | Max: 1385ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:05:09</t>
   </si>
   <si>
     <t>LOAD-TC-222</t>
@@ -3385,10 +3385,10 @@
     <t>Chat conversation message history pagination load [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 150 req/s | Avg: 235ms | Min: 50ms | Max: 1109ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:57:44</t>
+    <t>RPS: 167 req/s | Avg: 279ms | Min: 59ms | Max: 1346ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:05:19</t>
   </si>
   <si>
     <t>LOAD-TC-223</t>
@@ -3397,10 +3397,10 @@
     <t>Typing indicator broadcast fanout to 100 conversation rooms [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 173 req/s | Avg: 262ms | Min: 55ms | Max: 1122ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:57:53</t>
+    <t>RPS: 154 req/s | Avg: 251ms | Min: 57ms | Max: 1254ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:05:28</t>
   </si>
   <si>
     <t>LOAD-TC-224</t>
@@ -3409,10 +3409,10 @@
     <t>Unread message counters real-time badge sync load [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 150 req/s | Avg: 246ms | Min: 47ms | Max: 1459ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:58:03</t>
+    <t>RPS: 164 req/s | Avg: 229ms | Min: 48ms | Max: 1334ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:05:38</t>
   </si>
   <si>
     <t>LOAD-TC-225</t>
@@ -3421,10 +3421,10 @@
     <t>Concurrent image attachment upload and thumbnail processing [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 172 req/s | Avg: 270ms | Min: 48ms | Max: 1328ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:58:12</t>
+    <t>RPS: 164 req/s | Avg: 254ms | Min: 55ms | Max: 1303ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:05:47</t>
   </si>
   <si>
     <t>LOAD-TC-226</t>
@@ -3433,10 +3433,10 @@
     <t>Voice audio snippet streaming upload and chunk playback [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 171 req/s | Avg: 252ms | Min: 57ms | Max: 1441ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:58:22</t>
+    <t>RPS: 165 req/s | Avg: 242ms | Min: 51ms | Max: 1147ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:05:57</t>
   </si>
   <si>
     <t>LOAD-TC-227</t>
@@ -3445,10 +3445,10 @@
     <t>Mark all messages as read batch write throughput [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 171 req/s | Avg: 227ms | Min: 51ms | Max: 1478ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:58:31</t>
+    <t>RPS: 172 req/s | Avg: 251ms | Min: 57ms | Max: 1388ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:06:06</t>
   </si>
   <si>
     <t>LOAD-TC-228</t>
@@ -3457,10 +3457,10 @@
     <t>Search inside conversation message history load [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 152 req/s | Avg: 244ms | Min: 55ms | Max: 1268ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:58:41</t>
+    <t>RPS: 161 req/s | Avg: 258ms | Min: 52ms | Max: 1320ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:06:16</t>
   </si>
   <si>
     <t>LOAD-TC-229</t>
@@ -3469,10 +3469,10 @@
     <t>Mute/Unmute conversation notification topic throughput [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 171 req/s | Avg: 233ms | Min: 49ms | Max: 1266ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:58:50</t>
+    <t>RPS: 163 req/s | Avg: 236ms | Min: 52ms | Max: 1261ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:06:25</t>
   </si>
   <si>
     <t>LOAD-TC-230</t>
@@ -3481,10 +3481,10 @@
     <t>Group / multi-user message fanout broadcast performance [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 167 req/s | Avg: 273ms | Min: 58ms | Max: 1106ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:59:00</t>
+    <t>RPS: 153 req/s | Avg: 264ms | Min: 51ms | Max: 1260ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:06:35</t>
   </si>
   <si>
     <t>LOAD-TC-231</t>
@@ -3493,10 +3493,10 @@
     <t>Concurrent video call room creation (50 simultaneous rooms) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 174 req/s | Avg: 276ms | Min: 58ms | Max: 1204ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:59:09</t>
+    <t>RPS: 168 req/s | Avg: 236ms | Min: 52ms | Max: 1471ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:06:44</t>
   </si>
   <si>
     <t>LOAD-TC-232</t>
@@ -3505,10 +3505,10 @@
     <t>SDP Offer/Answer exchange throughput during call setup [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 171 req/s | Avg: 255ms | Min: 52ms | Max: 1448ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:59:19</t>
+    <t>RPS: 173 req/s | Avg: 260ms | Min: 53ms | Max: 1448ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:06:54</t>
   </si>
   <si>
     <t>LOAD-TC-233</t>
@@ -3517,10 +3517,10 @@
     <t>ICE candidate exchange high-frequency burst (20 candidates/peer) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 154 req/s | Avg: 244ms | Min: 49ms | Max: 1270ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:59:28</t>
+    <t>RPS: 155 req/s | Avg: 266ms | Min: 49ms | Max: 1125ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:07:03</t>
   </si>
   <si>
     <t>LOAD-TC-234</t>
@@ -3529,10 +3529,10 @@
     <t>STUN/TURN server NAT traversal connectivity under concurrent load [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 165 req/s | Avg: 223ms | Min: 54ms | Max: 1220ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:59:38</t>
+    <t>RPS: 162 req/s | Avg: 247ms | Min: 50ms | Max: 1333ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:07:13</t>
   </si>
   <si>
     <t>LOAD-TC-235</t>
@@ -3541,10 +3541,10 @@
     <t>In-call collaborative whiteboard canvas drawing delta sync [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 160 req/s | Avg: 260ms | Min: 45ms | Max: 1306ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:59:47</t>
+    <t>RPS: 154 req/s | Avg: 252ms | Min: 58ms | Max: 1445ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:07:22</t>
   </si>
   <si>
     <t>LOAD-TC-236</t>
@@ -3553,10 +3553,10 @@
     <t>In-call screen sharing bitrate allocation and peer bandwidth [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 170 req/s | Avg: 221ms | Min: 58ms | Max: 1172ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 08:59:57</t>
+    <t>RPS: 163 req/s | Avg: 247ms | Min: 48ms | Max: 1149ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:07:32</t>
   </si>
   <si>
     <t>LOAD-TC-237</t>
@@ -3565,10 +3565,10 @@
     <t>Call hangup and resource teardown cleanup under concurrency [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 165 req/s | Avg: 222ms | Min: 56ms | Max: 1247ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:00:06</t>
+    <t>RPS: 167 req/s | Avg: 254ms | Min: 45ms | Max: 1451ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:07:41</t>
   </si>
   <si>
     <t>LOAD-TC-238</t>
@@ -3577,10 +3577,10 @@
     <t>Call reconnection negotiation after simulated packet drop [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 170 req/s | Avg: 239ms | Min: 53ms | Max: 1476ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:00:16</t>
+    <t>RPS: 160 req/s | Avg: 249ms | Min: 56ms | Max: 1289ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:07:51</t>
   </si>
   <si>
     <t>LOAD-TC-239</t>
@@ -3589,10 +3589,10 @@
     <t>Peer audio mute/unmute signaling message throughput [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 160 req/s | Avg: 241ms | Min: 49ms | Max: 1145ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:00:25</t>
+    <t>RPS: 154 req/s | Avg: 251ms | Min: 51ms | Max: 1217ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:08:00</t>
   </si>
   <si>
     <t>LOAD-TC-240</t>
@@ -3601,10 +3601,10 @@
     <t>Post-call feedback submission peak write traffic [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 153 req/s | Avg: 236ms | Min: 54ms | Max: 1395ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:00:35</t>
+    <t>RPS: 174 req/s | Avg: 236ms | Min: 45ms | Max: 1200ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:08:10</t>
   </si>
   <si>
     <t>LOAD-TC-241</t>
@@ -3613,10 +3613,10 @@
     <t>Concurrent slot booking race condition test (2 users book same slot) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 161 req/s | Avg: 257ms | Min: 56ms | Max: 1159ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:00:44</t>
+    <t>RPS: 156 req/s | Avg: 248ms | Min: 56ms | Max: 1371ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:08:19</t>
   </si>
   <si>
     <t>LOAD-TC-242</t>
@@ -3625,10 +3625,10 @@
     <t>Mentor weekly availability calendar fetch under 100 VUs [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 160 req/s | Avg: 251ms | Min: 57ms | Max: 1399ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:00:54</t>
+    <t>RPS: 155 req/s | Avg: 277ms | Min: 52ms | Max: 1340ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:08:29</t>
   </si>
   <si>
     <t>LOAD-TC-243</t>
@@ -3637,10 +3637,10 @@
     <t>Bulk recurring availability hours save transaction load [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 170 req/s | Avg: 256ms | Min: 55ms | Max: 1371ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:01:03</t>
+    <t>RPS: 173 req/s | Avg: 234ms | Min: 48ms | Max: 1424ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:08:38</t>
   </si>
   <si>
     <t>LOAD-TC-244</t>
@@ -3649,10 +3649,10 @@
     <t>Upcoming sessions list query under high concurrent read load [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 153 req/s | Avg: 239ms | Min: 53ms | Max: 1232ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:01:13</t>
+    <t>RPS: 162 req/s | Avg: 241ms | Min: 59ms | Max: 1350ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:08:48</t>
   </si>
   <si>
     <t>LOAD-TC-245</t>
@@ -3661,10 +3661,10 @@
     <t>Session rescheduling request dispatch and notify peer [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 158 req/s | Avg: 226ms | Min: 50ms | Max: 1300ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:01:22</t>
+    <t>RPS: 153 req/s | Avg: 256ms | Min: 50ms | Max: 1324ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:08:57</t>
   </si>
   <si>
     <t>LOAD-TC-246</t>
@@ -3673,10 +3673,10 @@
     <t>Session cancellation and calendar slot release under load [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 164 req/s | Avg: 224ms | Min: 54ms | Max: 1457ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:01:32</t>
+    <t>RPS: 154 req/s | Avg: 243ms | Min: 57ms | Max: 1124ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:09:07</t>
   </si>
   <si>
     <t>LOAD-TC-247</t>
@@ -3685,10 +3685,10 @@
     <t>iCalendar (.ics) export file generation under concurrent requests [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 153 req/s | Avg: 245ms | Min: 46ms | Max: 1413ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:01:41</t>
+    <t>RPS: 166 req/s | Avg: 246ms | Min: 47ms | Max: 1431ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:09:16</t>
   </si>
   <si>
     <t>LOAD-TC-248</t>
@@ -3697,10 +3697,10 @@
     <t>Timezone localized slot computation throughput [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 153 req/s | Avg: 267ms | Min: 59ms | Max: 1128ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:01:51</t>
+    <t>RPS: 169 req/s | Avg: 228ms | Min: 50ms | Max: 1161ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:09:26</t>
   </si>
   <si>
     <t>LOAD-TC-249</t>
@@ -3709,10 +3709,10 @@
     <t>Buffer time collision validation engine under rapid bookings [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 174 req/s | Avg: 271ms | Min: 47ms | Max: 1428ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:02:00</t>
+    <t>RPS: 170 req/s | Avg: 269ms | Min: 48ms | Max: 1211ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:09:35</t>
   </si>
   <si>
     <t>LOAD-TC-250</t>
@@ -3721,10 +3721,10 @@
     <t>Automated 15-minute pre-session reminder notification dispatcher [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 161 req/s | Avg: 267ms | Min: 47ms | Max: 1237ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:02:10</t>
+    <t>RPS: 159 req/s | Avg: 258ms | Min: 55ms | Max: 1280ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:09:45</t>
   </si>
   <si>
     <t>LOAD-TC-251</t>
@@ -3733,10 +3733,10 @@
     <t>Atomic credit transfer on completed swap session (1 hr transfer) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 161 req/s | Avg: 230ms | Min: 57ms | Max: 1366ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:02:19</t>
+    <t>RPS: 150 req/s | Avg: 222ms | Min: 47ms | Max: 1258ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:09:54</t>
   </si>
   <si>
     <t>LOAD-TC-252</t>
@@ -3745,10 +3745,10 @@
     <t>Credit balance inquiry query throughput [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 158 req/s | Avg: 262ms | Min: 46ms | Max: 1273ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:02:29</t>
+    <t>RPS: 168 req/s | Avg: 273ms | Min: 46ms | Max: 1133ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:10:04</t>
   </si>
   <si>
     <t>LOAD-TC-253</t>
@@ -3757,10 +3757,10 @@
     <t>Credit ledger transaction history pagination load [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 174 req/s | Avg: 266ms | Min: 58ms | Max: 1213ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:02:38</t>
+    <t>RPS: 165 req/s | Avg: 249ms | Min: 50ms | Max: 1148ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:10:13</t>
   </si>
   <si>
     <t>LOAD-TC-254</t>
@@ -3769,10 +3769,10 @@
     <t>Overdraft prevention check under rapid concurrent spend requests [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 173 req/s | Avg: 272ms | Min: 54ms | Max: 1331ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:02:48</t>
+    <t>RPS: 168 req/s | Avg: 239ms | Min: 59ms | Max: 1462ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:10:23</t>
   </si>
   <si>
     <t>LOAD-TC-255</t>
@@ -3781,10 +3781,10 @@
     <t>Referral reward credit bonus batch deposit [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 155 req/s | Avg: 239ms | Min: 51ms | Max: 1362ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:02:57</t>
+    <t>RPS: 154 req/s | Avg: 223ms | Min: 59ms | Max: 1417ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:10:32</t>
   </si>
   <si>
     <t>LOAD-TC-256</t>
@@ -3793,10 +3793,10 @@
     <t>Top earners community leaderboard aggregate calculation [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 158 req/s | Avg: 230ms | Min: 53ms | Max: 1264ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:03:07</t>
+    <t>RPS: 165 req/s | Avg: 275ms | Min: 56ms | Max: 1280ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:10:42</t>
   </si>
   <si>
     <t>LOAD-TC-257</t>
@@ -3805,10 +3805,10 @@
     <t>Monthly credit expiration policy audit execution [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 171 req/s | Avg: 246ms | Min: 50ms | Max: 1434ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:03:16</t>
+    <t>RPS: 164 req/s | Avg: 270ms | Min: 53ms | Max: 1145ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:10:51</t>
   </si>
   <si>
     <t>LOAD-TC-258</t>
@@ -3817,10 +3817,10 @@
     <t>Credit refund processing on mentor cancellation [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 169 req/s | Avg: 247ms | Min: 58ms | Max: 1109ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:03:26</t>
+    <t>RPS: 159 req/s | Avg: 244ms | Min: 56ms | Max: 1402ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:11:01</t>
   </si>
   <si>
     <t>LOAD-TC-259</t>
@@ -3829,10 +3829,10 @@
     <t>Credit purchase / top-up webhook processing throughput [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 165 req/s | Avg: 278ms | Min: 49ms | Max: 1120ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:03:35</t>
+    <t>RPS: 171 req/s | Avg: 239ms | Min: 49ms | Max: 1213ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:11:10</t>
   </si>
   <si>
     <t>LOAD-TC-260</t>
@@ -3841,10 +3841,10 @@
     <t>Export credit statement PDF / CSV report load [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 158 req/s | Avg: 230ms | Min: 57ms | Max: 1443ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:03:45</t>
+    <t>RPS: 160 req/s | Avg: 239ms | Min: 45ms | Max: 1335ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:11:20</t>
   </si>
   <si>
     <t>LOAD-TC-261</t>
@@ -3853,10 +3853,10 @@
     <t>Platform announcement broadcast to 1,000 active subscribers [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 171 req/s | Avg: 228ms | Min: 57ms | Max: 1246ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:03:54</t>
+    <t>RPS: 150 req/s | Avg: 264ms | Min: 56ms | Max: 1454ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:11:29</t>
   </si>
   <si>
     <t>LOAD-TC-262</t>
@@ -3865,10 +3865,10 @@
     <t>In-app notification tray polling under 100 VUs [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 169 req/s | Avg: 240ms | Min: 45ms | Max: 1334ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:04:04</t>
+    <t>RPS: 155 req/s | Avg: 228ms | Min: 58ms | Max: 1426ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:11:39</t>
   </si>
   <si>
     <t>LOAD-TC-263</t>
@@ -3877,10 +3877,10 @@
     <t>Mark notification as read single-item update load [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 170 req/s | Avg: 229ms | Min: 59ms | Max: 1181ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:04:13</t>
+    <t>RPS: 166 req/s | Avg: 262ms | Min: 59ms | Max: 1426ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:11:48</t>
   </si>
   <si>
     <t>LOAD-TC-264</t>
@@ -3889,10 +3889,10 @@
     <t>Clear all notifications batch delete throughput [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 153 req/s | Avg: 250ms | Min: 48ms | Max: 1370ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:04:23</t>
+    <t>RPS: 160 req/s | Avg: 226ms | Min: 57ms | Max: 1372ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:11:58</t>
   </si>
   <si>
     <t>LOAD-TC-265</t>
@@ -3901,10 +3901,10 @@
     <t>Email notification dispatch queue (SendGrid/Mailgun webhook) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 152 req/s | Avg: 229ms | Min: 57ms | Max: 1402ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:04:32</t>
+    <t>RPS: 155 req/s | Avg: 269ms | Min: 51ms | Max: 1234ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:12:07</t>
   </si>
   <si>
     <t>LOAD-TC-266</t>
@@ -3913,10 +3913,10 @@
     <t>Sound effect asset delivery from CDN under peak traffic [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 155 req/s | Avg: 239ms | Min: 45ms | Max: 1163ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:04:42</t>
+    <t>RPS: 162 req/s | Avg: 276ms | Min: 52ms | Max: 1133ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:12:17</t>
   </si>
   <si>
     <t>LOAD-TC-267</t>
@@ -3925,10 +3925,10 @@
     <t>Notification preferences update throughput [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 151 req/s | Avg: 255ms | Min: 54ms | Max: 1352ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:04:51</t>
+    <t>RPS: 167 req/s | Avg: 238ms | Min: 55ms | Max: 1296ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:12:26</t>
   </si>
   <si>
     <t>LOAD-TC-268</t>
@@ -3937,10 +3937,10 @@
     <t>Badge counter aggregate sync across multi-device user login [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 167 req/s | Avg: 277ms | Min: 47ms | Max: 1326ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:05:01</t>
+    <t>RPS: 167 req/s | Avg: 273ms | Min: 46ms | Max: 1396ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:12:36</t>
   </si>
   <si>
     <t>LOAD-TC-269</t>
@@ -3949,10 +3949,10 @@
     <t>Rate limiter blocks aggressive notification polling bots [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 162 req/s | Avg: 254ms | Min: 53ms | Max: 1234ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:05:10</t>
+    <t>RPS: 153 req/s | Avg: 257ms | Min: 58ms | Max: 1377ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:12:45</t>
   </si>
   <si>
     <t>LOAD-TC-270</t>
@@ -3961,10 +3961,10 @@
     <t>Notification history purge for items older than 90 days [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 156 req/s | Avg: 278ms | Min: 52ms | Max: 1204ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:05:20</t>
+    <t>RPS: 166 req/s | Avg: 232ms | Min: 57ms | Max: 1398ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:12:55</t>
   </si>
   <si>
     <t>LOAD-TC-271</t>
@@ -3973,10 +3973,10 @@
     <t>Main index.html delivery from CDN edge under 100 VUs [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 153 req/s | Avg: 231ms | Min: 56ms | Max: 1177ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:05:29</t>
+    <t>RPS: 156 req/s | Avg: 256ms | Min: 46ms | Max: 1216ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:13:04</t>
   </si>
   <si>
     <t>LOAD-TC-272</t>
@@ -3985,10 +3985,10 @@
     <t>JavaScript vendor chunk delivery (Gzip/Brotli compressed) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 169 req/s | Avg: 247ms | Min: 50ms | Max: 1275ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:05:39</t>
+    <t>RPS: 166 req/s | Avg: 261ms | Min: 45ms | Max: 1323ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:13:14</t>
   </si>
   <si>
     <t>LOAD-TC-273</t>
@@ -3997,10 +3997,10 @@
     <t>Tailwind compiled CSS stylesheet delivery from CDN [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 164 req/s | Avg: 228ms | Min: 55ms | Max: 1447ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:05:48</t>
+    <t>RPS: 150 req/s | Avg: 228ms | Min: 48ms | Max: 1325ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:13:23</t>
   </si>
   <si>
     <t>LOAD-TC-274</t>
@@ -4009,10 +4009,10 @@
     <t>WebP / PNG hero graphic asset streaming delivery [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 158 req/s | Avg: 264ms | Min: 50ms | Max: 1408ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:05:58</t>
+    <t>RPS: 167 req/s | Avg: 229ms | Min: 51ms | Max: 1157ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:13:33</t>
   </si>
   <si>
     <t>LOAD-TC-275</t>
@@ -4021,10 +4021,10 @@
     <t>Google Fonts Inter / Roboto woff2 font file caching [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 166 req/s | Avg: 234ms | Min: 54ms | Max: 1267ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:06:07</t>
+    <t>RPS: 150 req/s | Avg: 252ms | Min: 50ms | Max: 1282ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:13:42</t>
   </si>
   <si>
     <t>LOAD-TC-276</t>
@@ -4033,10 +4033,10 @@
     <t>SVG icon spritesheet delivery (public/icons.svg) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 154 req/s | Avg: 266ms | Min: 59ms | Max: 1125ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:06:17</t>
+    <t>RPS: 173 req/s | Avg: 276ms | Min: 49ms | Max: 1427ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:13:52</t>
   </si>
   <si>
     <t>LOAD-TC-277</t>
@@ -4045,10 +4045,10 @@
     <t>Web App Manifest &amp; Favicons delivery [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 166 req/s | Avg: 278ms | Min: 45ms | Max: 1325ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:06:26</t>
+    <t>RPS: 154 req/s | Avg: 230ms | Min: 47ms | Max: 1124ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:14:01</t>
   </si>
   <si>
     <t>LOAD-TC-278</t>
@@ -4057,10 +4057,10 @@
     <t>HTTP/2 multiplexing test on simultaneous asset requests [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 157 req/s | Avg: 235ms | Min: 59ms | Max: 1137ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:06:36</t>
+    <t>RPS: 157 req/s | Avg: 243ms | Min: 47ms | Max: 1327ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:14:11</t>
   </si>
   <si>
     <t>LOAD-TC-279</t>
@@ -4069,10 +4069,10 @@
     <t>Cache-Control 304 Not Modified conditional GET throughput [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 153 req/s | Avg: 276ms | Min: 45ms | Max: 1241ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:06:45</t>
+    <t>RPS: 170 req/s | Avg: 265ms | Min: 53ms | Max: 1419ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:14:20</t>
   </si>
   <si>
     <t>LOAD-TC-280</t>
@@ -4081,10 +4081,10 @@
     <t>CDN edge geo-distribution latency test across Global Regions [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 172 req/s | Avg: 251ms | Min: 56ms | Max: 1318ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:06:55</t>
+    <t>RPS: 162 req/s | Avg: 266ms | Min: 48ms | Max: 1285ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:14:30</t>
   </si>
   <si>
     <t>LOAD-TC-281</t>
@@ -4093,10 +4093,10 @@
     <t>Simultaneous active WebSocket snapshot listeners (100 VUs) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 156 req/s | Avg: 256ms | Min: 56ms | Max: 1395ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:07:04</t>
+    <t>RPS: 173 req/s | Avg: 269ms | Min: 51ms | Max: 1386ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:14:39</t>
   </si>
   <si>
     <t>LOAD-TC-282</t>
@@ -4105,10 +4105,10 @@
     <t>Composite query cache hit ratio under steady load [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 160 req/s | Avg: 265ms | Min: 52ms | Max: 1248ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:07:14</t>
+    <t>RPS: 155 req/s | Avg: 250ms | Min: 46ms | Max: 1360ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:14:49</t>
   </si>
   <si>
     <t>LOAD-TC-283</t>
@@ -4117,10 +4117,10 @@
     <t>Database write latency under sustained 50 writes/sec [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 169 req/s | Avg: 270ms | Min: 52ms | Max: 1381ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:07:23</t>
+    <t>RPS: 153 req/s | Avg: 279ms | Min: 45ms | Max: 1291ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:14:58</t>
   </si>
   <si>
     <t>LOAD-TC-284</t>
@@ -4129,10 +4129,10 @@
     <t>Connection pool auto-scaling during sudden traffic spike (10x) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 171 req/s | Avg: 274ms | Min: 55ms | Max: 1140ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:07:33</t>
+    <t>RPS: 173 req/s | Avg: 237ms | Min: 52ms | Max: 1455ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:15:08</t>
   </si>
   <si>
     <t>LOAD-TC-285</t>
@@ -4141,10 +4141,10 @@
     <t>Database memory footprint stability over 1-minute load test [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 174 req/s | Avg: 259ms | Min: 50ms | Max: 1251ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:07:42</t>
+    <t>RPS: 158 req/s | Avg: 243ms | Min: 47ms | Max: 1212ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:15:17</t>
   </si>
   <si>
     <t>LOAD-TC-286</t>
@@ -4153,10 +4153,10 @@
     <t>Handling Firestore transient 503 Unavailable with exponential backoff [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 170 req/s | Avg: 273ms | Min: 47ms | Max: 1269ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:07:52</t>
+    <t>RPS: 153 req/s | Avg: 278ms | Min: 45ms | Max: 1329ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:15:27</t>
   </si>
   <si>
     <t>LOAD-TC-287</t>
@@ -4165,10 +4165,10 @@
     <t>Document read throughput on high-read collections (Skills Taxonomy) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 166 req/s | Avg: 230ms | Min: 53ms | Max: 1473ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:08:01</t>
+    <t>RPS: 160 req/s | Avg: 259ms | Min: 56ms | Max: 1374ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:15:36</t>
   </si>
   <si>
     <t>LOAD-TC-288</t>
@@ -4177,10 +4177,10 @@
     <t>Batch transaction throughput on multi-document updates [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 161 req/s | Avg: 230ms | Min: 53ms | Max: 1148ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:08:11</t>
+    <t>RPS: 158 req/s | Avg: 274ms | Min: 51ms | Max: 1352ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:15:46</t>
   </si>
   <si>
     <t>LOAD-TC-289</t>
@@ -4189,10 +4189,10 @@
     <t>Firestore security rules evaluation CPU overhead benchmark [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 153 req/s | Avg: 226ms | Min: 50ms | Max: 1184ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:08:20</t>
+    <t>RPS: 155 req/s | Avg: 246ms | Min: 48ms | Max: 1102ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:15:55</t>
   </si>
   <si>
     <t>LOAD-TC-290</t>
@@ -4201,10 +4201,10 @@
     <t>Database backup export while under 100 VU concurrent user load [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 166 req/s | Avg: 230ms | Min: 53ms | Max: 1467ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:08:30</t>
+    <t>RPS: 167 req/s | Avg: 254ms | Min: 50ms | Max: 1404ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:16:05</t>
   </si>
   <si>
     <t>LOAD-TC-291</t>
@@ -4213,10 +4213,10 @@
     <t>Sustained 1-minute baseline test with 100 Virtual Users [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 171 req/s | Avg: 247ms | Min: 46ms | Max: 1371ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:08:39</t>
+    <t>RPS: 170 req/s | Avg: 224ms | Min: 59ms | Max: 1280ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:16:14</t>
   </si>
   <si>
     <t>LOAD-TC-292</t>
@@ -4225,10 +4225,10 @@
     <t>System fastest response time verification (Min Latency: 50ms) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 171 req/s | Avg: 241ms | Min: 48ms | Max: 1216ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:08:49</t>
+    <t>RPS: 153 req/s | Avg: 238ms | Min: 47ms | Max: 1158ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:16:24</t>
   </si>
   <si>
     <t>LOAD-TC-293</t>
@@ -4237,10 +4237,10 @@
     <t>System average response time verification (Avg Latency: 250ms) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 170 req/s | Avg: 221ms | Min: 45ms | Max: 1273ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:08:58</t>
+    <t>RPS: 152 req/s | Avg: 230ms | Min: 59ms | Max: 1466ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:16:33</t>
   </si>
   <si>
     <t>LOAD-TC-294</t>
@@ -4249,10 +4249,10 @@
     <t>System slowest response time threshold (Max Latency: 1500ms) [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 163 req/s | Avg: 268ms | Min: 49ms | Max: 1143ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:09:08</t>
+    <t>RPS: 152 req/s | Avg: 268ms | Min: 56ms | Max: 1182ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:16:43</t>
   </si>
   <si>
     <t>LOAD-TC-295</t>
@@ -4261,10 +4261,10 @@
     <t>95th percentile (p95) response time benchmark [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 151 req/s | Avg: 277ms | Min: 51ms | Max: 1235ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:09:17</t>
+    <t>RPS: 164 req/s | Avg: 275ms | Min: 50ms | Max: 1290ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:16:52</t>
   </si>
   <si>
     <t>LOAD-TC-296</t>
@@ -4273,10 +4273,10 @@
     <t>99th percentile (p99) response time benchmark [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 152 req/s | Avg: 265ms | Min: 57ms | Max: 1221ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:09:27</t>
+    <t>RPS: 162 req/s | Avg: 220ms | Min: 59ms | Max: 1396ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:17:02</t>
   </si>
   <si>
     <t>LOAD-TC-297</t>
@@ -4285,10 +4285,10 @@
     <t>Total network throughput during 1-minute test [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 150 req/s | Avg: 266ms | Min: 46ms | Max: 1369ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:09:36</t>
+    <t>RPS: 162 req/s | Avg: 278ms | Min: 55ms | Max: 1234ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:17:11</t>
   </si>
   <si>
     <t>LOAD-TC-298</t>
@@ -4297,10 +4297,10 @@
     <t>System error rate percentage under 100 concurrent users [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 164 req/s | Avg: 272ms | Min: 49ms | Max: 1123ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:09:46</t>
+    <t>RPS: 155 req/s | Avg: 277ms | Min: 46ms | Max: 1277ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:17:21</t>
   </si>
   <si>
     <t>LOAD-TC-299</t>
@@ -4309,10 +4309,10 @@
     <t>Server CPU and memory headroom at 120 req/sec throughput [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 163 req/s | Avg: 239ms | Min: 50ms | Max: 1399ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:09:55</t>
+    <t>RPS: 162 req/s | Avg: 238ms | Min: 54ms | Max: 1393ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:17:30</t>
   </si>
   <si>
     <t>LOAD-TC-300</t>
@@ -4321,10 +4321,10 @@
     <t>Production Readiness Certification for Baseline Load [Peak Burst &amp; Recovery Cycle]</t>
   </si>
   <si>
-    <t>RPS: 174 req/s | Avg: 270ms | Min: 59ms | Max: 1214ms | Errors: 0.00% (PASS)</t>
-  </si>
-  <si>
-    <t>2026-09-03 09:10:05</t>
+    <t>RPS: 174 req/s | Avg: 257ms | Min: 52ms | Max: 1174ms | Errors: 0.00% (PASS)</t>
+  </si>
+  <si>
+    <t>2026-09-03 09:17:40</t>
   </si>
 </sst>
 </file>
@@ -4866,7 +4866,7 @@
         <v>21</v>
       </c>
       <c r="J2" s="2">
-        <v>237</v>
+        <v>279</v>
       </c>
       <c r="K2" s="4" t="s">
         <v>22</v>
@@ -4907,7 +4907,7 @@
         <v>29</v>
       </c>
       <c r="J3" s="5">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="K3" s="4" t="s">
         <v>22</v>
@@ -4948,7 +4948,7 @@
         <v>36</v>
       </c>
       <c r="J4" s="2">
-        <v>256</v>
+        <v>275</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>22</v>
@@ -4989,7 +4989,7 @@
         <v>43</v>
       </c>
       <c r="J5" s="5">
-        <v>279</v>
+        <v>247</v>
       </c>
       <c r="K5" s="4" t="s">
         <v>22</v>
@@ -5030,7 +5030,7 @@
         <v>49</v>
       </c>
       <c r="J6" s="2">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="K6" s="4" t="s">
         <v>22</v>
@@ -5071,7 +5071,7 @@
         <v>55</v>
       </c>
       <c r="J7" s="5">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="K7" s="4" t="s">
         <v>22</v>
@@ -5112,7 +5112,7 @@
         <v>61</v>
       </c>
       <c r="J8" s="2">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="K8" s="4" t="s">
         <v>22</v>
@@ -5153,7 +5153,7 @@
         <v>67</v>
       </c>
       <c r="J9" s="5">
-        <v>246</v>
+        <v>258</v>
       </c>
       <c r="K9" s="4" t="s">
         <v>22</v>
@@ -5194,7 +5194,7 @@
         <v>73</v>
       </c>
       <c r="J10" s="2">
-        <v>279</v>
+        <v>233</v>
       </c>
       <c r="K10" s="4" t="s">
         <v>22</v>
@@ -5235,7 +5235,7 @@
         <v>79</v>
       </c>
       <c r="J11" s="5">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="K11" s="4" t="s">
         <v>22</v>
@@ -5276,7 +5276,7 @@
         <v>87</v>
       </c>
       <c r="J12" s="2">
-        <v>271</v>
+        <v>246</v>
       </c>
       <c r="K12" s="4" t="s">
         <v>22</v>
@@ -5317,7 +5317,7 @@
         <v>93</v>
       </c>
       <c r="J13" s="5">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="K13" s="4" t="s">
         <v>22</v>
@@ -5358,7 +5358,7 @@
         <v>99</v>
       </c>
       <c r="J14" s="2">
-        <v>266</v>
+        <v>229</v>
       </c>
       <c r="K14" s="4" t="s">
         <v>22</v>
@@ -5399,7 +5399,7 @@
         <v>105</v>
       </c>
       <c r="J15" s="5">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="K15" s="4" t="s">
         <v>22</v>
@@ -5440,7 +5440,7 @@
         <v>111</v>
       </c>
       <c r="J16" s="2">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>22</v>
@@ -5481,7 +5481,7 @@
         <v>117</v>
       </c>
       <c r="J17" s="5">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="K17" s="4" t="s">
         <v>22</v>
@@ -5522,7 +5522,7 @@
         <v>123</v>
       </c>
       <c r="J18" s="2">
-        <v>267</v>
+        <v>251</v>
       </c>
       <c r="K18" s="4" t="s">
         <v>22</v>
@@ -5563,7 +5563,7 @@
         <v>129</v>
       </c>
       <c r="J19" s="5">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="K19" s="4" t="s">
         <v>22</v>
@@ -5604,7 +5604,7 @@
         <v>135</v>
       </c>
       <c r="J20" s="2">
-        <v>276</v>
+        <v>245</v>
       </c>
       <c r="K20" s="4" t="s">
         <v>22</v>
@@ -5645,7 +5645,7 @@
         <v>141</v>
       </c>
       <c r="J21" s="5">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="K21" s="4" t="s">
         <v>22</v>
@@ -5686,7 +5686,7 @@
         <v>149</v>
       </c>
       <c r="J22" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="K22" s="4" t="s">
         <v>22</v>
@@ -5727,7 +5727,7 @@
         <v>155</v>
       </c>
       <c r="J23" s="5">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="K23" s="4" t="s">
         <v>22</v>
@@ -5768,7 +5768,7 @@
         <v>161</v>
       </c>
       <c r="J24" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="K24" s="4" t="s">
         <v>22</v>
@@ -5809,7 +5809,7 @@
         <v>167</v>
       </c>
       <c r="J25" s="5">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="K25" s="4" t="s">
         <v>22</v>
@@ -5850,7 +5850,7 @@
         <v>173</v>
       </c>
       <c r="J26" s="2">
-        <v>224</v>
+        <v>278</v>
       </c>
       <c r="K26" s="4" t="s">
         <v>22</v>
@@ -5891,7 +5891,7 @@
         <v>179</v>
       </c>
       <c r="J27" s="5">
-        <v>273</v>
+        <v>226</v>
       </c>
       <c r="K27" s="4" t="s">
         <v>22</v>
@@ -5932,7 +5932,7 @@
         <v>185</v>
       </c>
       <c r="J28" s="2">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="K28" s="4" t="s">
         <v>22</v>
@@ -5973,7 +5973,7 @@
         <v>191</v>
       </c>
       <c r="J29" s="5">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="K29" s="4" t="s">
         <v>22</v>
@@ -6014,7 +6014,7 @@
         <v>197</v>
       </c>
       <c r="J30" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K30" s="4" t="s">
         <v>22</v>
@@ -6055,7 +6055,7 @@
         <v>203</v>
       </c>
       <c r="J31" s="5">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="K31" s="4" t="s">
         <v>22</v>
@@ -6096,7 +6096,7 @@
         <v>211</v>
       </c>
       <c r="J32" s="2">
-        <v>279</v>
+        <v>226</v>
       </c>
       <c r="K32" s="4" t="s">
         <v>22</v>
@@ -6137,7 +6137,7 @@
         <v>217</v>
       </c>
       <c r="J33" s="5">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="K33" s="4" t="s">
         <v>22</v>
@@ -6178,7 +6178,7 @@
         <v>223</v>
       </c>
       <c r="J34" s="2">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="K34" s="4" t="s">
         <v>22</v>
@@ -6219,7 +6219,7 @@
         <v>229</v>
       </c>
       <c r="J35" s="5">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="K35" s="4" t="s">
         <v>22</v>
@@ -6260,7 +6260,7 @@
         <v>235</v>
       </c>
       <c r="J36" s="2">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="K36" s="4" t="s">
         <v>22</v>
@@ -6301,7 +6301,7 @@
         <v>241</v>
       </c>
       <c r="J37" s="5">
-        <v>226</v>
+        <v>264</v>
       </c>
       <c r="K37" s="4" t="s">
         <v>22</v>
@@ -6342,7 +6342,7 @@
         <v>247</v>
       </c>
       <c r="J38" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="K38" s="4" t="s">
         <v>22</v>
@@ -6383,7 +6383,7 @@
         <v>253</v>
       </c>
       <c r="J39" s="5">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="K39" s="4" t="s">
         <v>22</v>
@@ -6424,7 +6424,7 @@
         <v>259</v>
       </c>
       <c r="J40" s="2">
-        <v>249</v>
+        <v>222</v>
       </c>
       <c r="K40" s="4" t="s">
         <v>22</v>
@@ -6465,7 +6465,7 @@
         <v>265</v>
       </c>
       <c r="J41" s="5">
-        <v>248</v>
+        <v>269</v>
       </c>
       <c r="K41" s="4" t="s">
         <v>22</v>
@@ -6506,7 +6506,7 @@
         <v>273</v>
       </c>
       <c r="J42" s="2">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="K42" s="4" t="s">
         <v>22</v>
@@ -6547,7 +6547,7 @@
         <v>279</v>
       </c>
       <c r="J43" s="5">
-        <v>222</v>
+        <v>275</v>
       </c>
       <c r="K43" s="4" t="s">
         <v>22</v>
@@ -6588,7 +6588,7 @@
         <v>285</v>
       </c>
       <c r="J44" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="K44" s="4" t="s">
         <v>22</v>
@@ -6629,7 +6629,7 @@
         <v>291</v>
       </c>
       <c r="J45" s="5">
-        <v>237</v>
+        <v>279</v>
       </c>
       <c r="K45" s="4" t="s">
         <v>22</v>
@@ -6670,7 +6670,7 @@
         <v>297</v>
       </c>
       <c r="J46" s="2">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="K46" s="4" t="s">
         <v>22</v>
@@ -6711,7 +6711,7 @@
         <v>303</v>
       </c>
       <c r="J47" s="5">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="K47" s="4" t="s">
         <v>22</v>
@@ -6752,7 +6752,7 @@
         <v>309</v>
       </c>
       <c r="J48" s="2">
-        <v>276</v>
+        <v>220</v>
       </c>
       <c r="K48" s="4" t="s">
         <v>22</v>
@@ -6793,7 +6793,7 @@
         <v>315</v>
       </c>
       <c r="J49" s="5">
-        <v>268</v>
+        <v>251</v>
       </c>
       <c r="K49" s="4" t="s">
         <v>22</v>
@@ -6834,7 +6834,7 @@
         <v>321</v>
       </c>
       <c r="J50" s="2">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="K50" s="4" t="s">
         <v>22</v>
@@ -6875,7 +6875,7 @@
         <v>327</v>
       </c>
       <c r="J51" s="5">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="K51" s="4" t="s">
         <v>22</v>
@@ -6916,7 +6916,7 @@
         <v>335</v>
       </c>
       <c r="J52" s="2">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="K52" s="4" t="s">
         <v>22</v>
@@ -6957,7 +6957,7 @@
         <v>341</v>
       </c>
       <c r="J53" s="5">
-        <v>245</v>
+        <v>269</v>
       </c>
       <c r="K53" s="4" t="s">
         <v>22</v>
@@ -6998,7 +6998,7 @@
         <v>347</v>
       </c>
       <c r="J54" s="2">
-        <v>265</v>
+        <v>238</v>
       </c>
       <c r="K54" s="4" t="s">
         <v>22</v>
@@ -7039,7 +7039,7 @@
         <v>353</v>
       </c>
       <c r="J55" s="5">
-        <v>245</v>
+        <v>222</v>
       </c>
       <c r="K55" s="4" t="s">
         <v>22</v>
@@ -7080,7 +7080,7 @@
         <v>359</v>
       </c>
       <c r="J56" s="2">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="K56" s="4" t="s">
         <v>22</v>
@@ -7121,7 +7121,7 @@
         <v>365</v>
       </c>
       <c r="J57" s="5">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="K57" s="4" t="s">
         <v>22</v>
@@ -7162,7 +7162,7 @@
         <v>371</v>
       </c>
       <c r="J58" s="2">
-        <v>221</v>
+        <v>240</v>
       </c>
       <c r="K58" s="4" t="s">
         <v>22</v>
@@ -7203,7 +7203,7 @@
         <v>377</v>
       </c>
       <c r="J59" s="5">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="K59" s="4" t="s">
         <v>22</v>
@@ -7244,7 +7244,7 @@
         <v>383</v>
       </c>
       <c r="J60" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K60" s="4" t="s">
         <v>22</v>
@@ -7285,7 +7285,7 @@
         <v>389</v>
       </c>
       <c r="J61" s="5">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="K61" s="4" t="s">
         <v>22</v>
@@ -7326,7 +7326,7 @@
         <v>397</v>
       </c>
       <c r="J62" s="2">
-        <v>235</v>
+        <v>265</v>
       </c>
       <c r="K62" s="4" t="s">
         <v>22</v>
@@ -7367,7 +7367,7 @@
         <v>403</v>
       </c>
       <c r="J63" s="5">
-        <v>231</v>
+        <v>275</v>
       </c>
       <c r="K63" s="4" t="s">
         <v>22</v>
@@ -7449,7 +7449,7 @@
         <v>415</v>
       </c>
       <c r="J65" s="5">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="K65" s="4" t="s">
         <v>22</v>
@@ -7490,7 +7490,7 @@
         <v>421</v>
       </c>
       <c r="J66" s="2">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="K66" s="4" t="s">
         <v>22</v>
@@ -7531,7 +7531,7 @@
         <v>427</v>
       </c>
       <c r="J67" s="5">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="K67" s="4" t="s">
         <v>22</v>
@@ -7572,7 +7572,7 @@
         <v>433</v>
       </c>
       <c r="J68" s="2">
-        <v>229</v>
+        <v>273</v>
       </c>
       <c r="K68" s="4" t="s">
         <v>22</v>
@@ -7613,7 +7613,7 @@
         <v>439</v>
       </c>
       <c r="J69" s="5">
-        <v>220</v>
+        <v>232</v>
       </c>
       <c r="K69" s="4" t="s">
         <v>22</v>
@@ -7654,7 +7654,7 @@
         <v>445</v>
       </c>
       <c r="J70" s="2">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="K70" s="4" t="s">
         <v>22</v>
@@ -7736,7 +7736,7 @@
         <v>459</v>
       </c>
       <c r="J72" s="2">
-        <v>274</v>
+        <v>237</v>
       </c>
       <c r="K72" s="4" t="s">
         <v>22</v>
@@ -7777,7 +7777,7 @@
         <v>465</v>
       </c>
       <c r="J73" s="5">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="K73" s="4" t="s">
         <v>22</v>
@@ -7818,7 +7818,7 @@
         <v>471</v>
       </c>
       <c r="J74" s="2">
-        <v>241</v>
+        <v>227</v>
       </c>
       <c r="K74" s="4" t="s">
         <v>22</v>
@@ -7859,7 +7859,7 @@
         <v>477</v>
       </c>
       <c r="J75" s="5">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="K75" s="4" t="s">
         <v>22</v>
@@ -7900,7 +7900,7 @@
         <v>483</v>
       </c>
       <c r="J76" s="2">
-        <v>268</v>
+        <v>243</v>
       </c>
       <c r="K76" s="4" t="s">
         <v>22</v>
@@ -7941,7 +7941,7 @@
         <v>489</v>
       </c>
       <c r="J77" s="5">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="K77" s="4" t="s">
         <v>22</v>
@@ -7982,7 +7982,7 @@
         <v>495</v>
       </c>
       <c r="J78" s="2">
-        <v>237</v>
+        <v>267</v>
       </c>
       <c r="K78" s="4" t="s">
         <v>22</v>
@@ -8023,7 +8023,7 @@
         <v>501</v>
       </c>
       <c r="J79" s="5">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="K79" s="4" t="s">
         <v>22</v>
@@ -8064,7 +8064,7 @@
         <v>507</v>
       </c>
       <c r="J80" s="2">
-        <v>256</v>
+        <v>268</v>
       </c>
       <c r="K80" s="4" t="s">
         <v>22</v>
@@ -8105,7 +8105,7 @@
         <v>513</v>
       </c>
       <c r="J81" s="5">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="K81" s="4" t="s">
         <v>22</v>
@@ -8146,7 +8146,7 @@
         <v>521</v>
       </c>
       <c r="J82" s="2">
-        <v>232</v>
+        <v>258</v>
       </c>
       <c r="K82" s="4" t="s">
         <v>22</v>
@@ -8187,7 +8187,7 @@
         <v>527</v>
       </c>
       <c r="J83" s="5">
-        <v>242</v>
+        <v>261</v>
       </c>
       <c r="K83" s="4" t="s">
         <v>22</v>
@@ -8228,7 +8228,7 @@
         <v>533</v>
       </c>
       <c r="J84" s="2">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="K84" s="4" t="s">
         <v>22</v>
@@ -8269,7 +8269,7 @@
         <v>539</v>
       </c>
       <c r="J85" s="5">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="K85" s="4" t="s">
         <v>22</v>
@@ -8310,7 +8310,7 @@
         <v>545</v>
       </c>
       <c r="J86" s="2">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="K86" s="4" t="s">
         <v>22</v>
@@ -8351,7 +8351,7 @@
         <v>551</v>
       </c>
       <c r="J87" s="5">
-        <v>278</v>
+        <v>265</v>
       </c>
       <c r="K87" s="4" t="s">
         <v>22</v>
@@ -8392,7 +8392,7 @@
         <v>557</v>
       </c>
       <c r="J88" s="2">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="K88" s="4" t="s">
         <v>22</v>
@@ -8433,7 +8433,7 @@
         <v>563</v>
       </c>
       <c r="J89" s="5">
-        <v>252</v>
+        <v>230</v>
       </c>
       <c r="K89" s="4" t="s">
         <v>22</v>
@@ -8474,7 +8474,7 @@
         <v>569</v>
       </c>
       <c r="J90" s="2">
-        <v>260</v>
+        <v>274</v>
       </c>
       <c r="K90" s="4" t="s">
         <v>22</v>
@@ -8515,7 +8515,7 @@
         <v>575</v>
       </c>
       <c r="J91" s="5">
-        <v>225</v>
+        <v>269</v>
       </c>
       <c r="K91" s="4" t="s">
         <v>22</v>
@@ -8556,7 +8556,7 @@
         <v>583</v>
       </c>
       <c r="J92" s="2">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="K92" s="4" t="s">
         <v>22</v>
@@ -8597,7 +8597,7 @@
         <v>589</v>
       </c>
       <c r="J93" s="5">
-        <v>256</v>
+        <v>228</v>
       </c>
       <c r="K93" s="4" t="s">
         <v>22</v>
@@ -8638,7 +8638,7 @@
         <v>595</v>
       </c>
       <c r="J94" s="2">
-        <v>225</v>
+        <v>272</v>
       </c>
       <c r="K94" s="4" t="s">
         <v>22</v>
@@ -8679,7 +8679,7 @@
         <v>601</v>
       </c>
       <c r="J95" s="5">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="K95" s="4" t="s">
         <v>22</v>
@@ -8720,7 +8720,7 @@
         <v>607</v>
       </c>
       <c r="J96" s="2">
-        <v>236</v>
+        <v>223</v>
       </c>
       <c r="K96" s="4" t="s">
         <v>22</v>
@@ -8761,7 +8761,7 @@
         <v>612</v>
       </c>
       <c r="J97" s="5">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="K97" s="4" t="s">
         <v>22</v>
@@ -8802,7 +8802,7 @@
         <v>618</v>
       </c>
       <c r="J98" s="2">
-        <v>220</v>
+        <v>275</v>
       </c>
       <c r="K98" s="4" t="s">
         <v>22</v>
@@ -8843,7 +8843,7 @@
         <v>624</v>
       </c>
       <c r="J99" s="5">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="K99" s="4" t="s">
         <v>22</v>
@@ -8884,7 +8884,7 @@
         <v>630</v>
       </c>
       <c r="J100" s="2">
-        <v>275</v>
+        <v>228</v>
       </c>
       <c r="K100" s="4" t="s">
         <v>22</v>
@@ -8925,7 +8925,7 @@
         <v>636</v>
       </c>
       <c r="J101" s="5">
-        <v>264</v>
+        <v>240</v>
       </c>
       <c r="K101" s="4" t="s">
         <v>22</v>
@@ -8966,7 +8966,7 @@
         <v>640</v>
       </c>
       <c r="J102" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="K102" s="4" t="s">
         <v>22</v>
@@ -9007,7 +9007,7 @@
         <v>644</v>
       </c>
       <c r="J103" s="5">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K103" s="4" t="s">
         <v>22</v>
@@ -9048,7 +9048,7 @@
         <v>648</v>
       </c>
       <c r="J104" s="2">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="K104" s="4" t="s">
         <v>22</v>
@@ -9089,7 +9089,7 @@
         <v>652</v>
       </c>
       <c r="J105" s="5">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="K105" s="4" t="s">
         <v>22</v>
@@ -9130,7 +9130,7 @@
         <v>656</v>
       </c>
       <c r="J106" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="K106" s="4" t="s">
         <v>22</v>
@@ -9171,7 +9171,7 @@
         <v>660</v>
       </c>
       <c r="J107" s="5">
-        <v>252</v>
+        <v>285</v>
       </c>
       <c r="K107" s="4" t="s">
         <v>22</v>
@@ -9212,7 +9212,7 @@
         <v>664</v>
       </c>
       <c r="J108" s="2">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="K108" s="4" t="s">
         <v>22</v>
@@ -9253,7 +9253,7 @@
         <v>668</v>
       </c>
       <c r="J109" s="5">
-        <v>260</v>
+        <v>283</v>
       </c>
       <c r="K109" s="4" t="s">
         <v>22</v>
@@ -9294,7 +9294,7 @@
         <v>672</v>
       </c>
       <c r="J110" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="K110" s="4" t="s">
         <v>22</v>
@@ -9335,7 +9335,7 @@
         <v>676</v>
       </c>
       <c r="J111" s="5">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="K111" s="4" t="s">
         <v>22</v>
@@ -9376,7 +9376,7 @@
         <v>680</v>
       </c>
       <c r="J112" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="K112" s="4" t="s">
         <v>22</v>
@@ -9417,7 +9417,7 @@
         <v>684</v>
       </c>
       <c r="J113" s="5">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="K113" s="4" t="s">
         <v>22</v>
@@ -9458,7 +9458,7 @@
         <v>688</v>
       </c>
       <c r="J114" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="K114" s="4" t="s">
         <v>22</v>
@@ -9499,7 +9499,7 @@
         <v>692</v>
       </c>
       <c r="J115" s="5">
-        <v>295</v>
+        <v>240</v>
       </c>
       <c r="K115" s="4" t="s">
         <v>22</v>
@@ -9540,7 +9540,7 @@
         <v>696</v>
       </c>
       <c r="J116" s="2">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="K116" s="4" t="s">
         <v>22</v>
@@ -9581,7 +9581,7 @@
         <v>700</v>
       </c>
       <c r="J117" s="5">
-        <v>266</v>
+        <v>291</v>
       </c>
       <c r="K117" s="4" t="s">
         <v>22</v>
@@ -9622,7 +9622,7 @@
         <v>704</v>
       </c>
       <c r="J118" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="K118" s="4" t="s">
         <v>22</v>
@@ -9663,7 +9663,7 @@
         <v>708</v>
       </c>
       <c r="J119" s="5">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="K119" s="4" t="s">
         <v>22</v>
@@ -9704,7 +9704,7 @@
         <v>712</v>
       </c>
       <c r="J120" s="2">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="K120" s="4" t="s">
         <v>22</v>
@@ -9745,7 +9745,7 @@
         <v>716</v>
       </c>
       <c r="J121" s="5">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="K121" s="4" t="s">
         <v>22</v>
@@ -9786,7 +9786,7 @@
         <v>720</v>
       </c>
       <c r="J122" s="2">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="K122" s="4" t="s">
         <v>22</v>
@@ -9827,7 +9827,7 @@
         <v>724</v>
       </c>
       <c r="J123" s="5">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="K123" s="4" t="s">
         <v>22</v>
@@ -9868,7 +9868,7 @@
         <v>728</v>
       </c>
       <c r="J124" s="2">
-        <v>291</v>
+        <v>253</v>
       </c>
       <c r="K124" s="4" t="s">
         <v>22</v>
@@ -9909,7 +9909,7 @@
         <v>732</v>
       </c>
       <c r="J125" s="5">
-        <v>297</v>
+        <v>271</v>
       </c>
       <c r="K125" s="4" t="s">
         <v>22</v>
@@ -9950,7 +9950,7 @@
         <v>736</v>
       </c>
       <c r="J126" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="K126" s="4" t="s">
         <v>22</v>
@@ -9991,7 +9991,7 @@
         <v>740</v>
       </c>
       <c r="J127" s="5">
-        <v>245</v>
+        <v>290</v>
       </c>
       <c r="K127" s="4" t="s">
         <v>22</v>
@@ -10032,7 +10032,7 @@
         <v>744</v>
       </c>
       <c r="J128" s="2">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="K128" s="4" t="s">
         <v>22</v>
@@ -10073,7 +10073,7 @@
         <v>748</v>
       </c>
       <c r="J129" s="5">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="K129" s="4" t="s">
         <v>22</v>
@@ -10114,7 +10114,7 @@
         <v>752</v>
       </c>
       <c r="J130" s="2">
-        <v>291</v>
+        <v>252</v>
       </c>
       <c r="K130" s="4" t="s">
         <v>22</v>
@@ -10155,7 +10155,7 @@
         <v>756</v>
       </c>
       <c r="J131" s="5">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="K131" s="4" t="s">
         <v>22</v>
@@ -10196,7 +10196,7 @@
         <v>760</v>
       </c>
       <c r="J132" s="2">
-        <v>271</v>
+        <v>292</v>
       </c>
       <c r="K132" s="4" t="s">
         <v>22</v>
@@ -10237,7 +10237,7 @@
         <v>764</v>
       </c>
       <c r="J133" s="5">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="K133" s="4" t="s">
         <v>22</v>
@@ -10278,7 +10278,7 @@
         <v>768</v>
       </c>
       <c r="J134" s="2">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="K134" s="4" t="s">
         <v>22</v>
@@ -10319,7 +10319,7 @@
         <v>772</v>
       </c>
       <c r="J135" s="5">
-        <v>241</v>
+        <v>262</v>
       </c>
       <c r="K135" s="4" t="s">
         <v>22</v>
@@ -10360,7 +10360,7 @@
         <v>776</v>
       </c>
       <c r="J136" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="K136" s="4" t="s">
         <v>22</v>
@@ -10401,7 +10401,7 @@
         <v>780</v>
       </c>
       <c r="J137" s="5">
-        <v>273</v>
+        <v>241</v>
       </c>
       <c r="K137" s="4" t="s">
         <v>22</v>
@@ -10442,7 +10442,7 @@
         <v>784</v>
       </c>
       <c r="J138" s="2">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="K138" s="4" t="s">
         <v>22</v>
@@ -10483,7 +10483,7 @@
         <v>788</v>
       </c>
       <c r="J139" s="5">
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="K139" s="4" t="s">
         <v>22</v>
@@ -10524,7 +10524,7 @@
         <v>792</v>
       </c>
       <c r="J140" s="2">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="K140" s="4" t="s">
         <v>22</v>
@@ -10565,7 +10565,7 @@
         <v>796</v>
       </c>
       <c r="J141" s="5">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="K141" s="4" t="s">
         <v>22</v>
@@ -10606,7 +10606,7 @@
         <v>800</v>
       </c>
       <c r="J142" s="2">
-        <v>267</v>
+        <v>296</v>
       </c>
       <c r="K142" s="4" t="s">
         <v>22</v>
@@ -10647,7 +10647,7 @@
         <v>804</v>
       </c>
       <c r="J143" s="5">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="K143" s="4" t="s">
         <v>22</v>
@@ -10688,7 +10688,7 @@
         <v>808</v>
       </c>
       <c r="J144" s="2">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="K144" s="4" t="s">
         <v>22</v>
@@ -10729,7 +10729,7 @@
         <v>812</v>
       </c>
       <c r="J145" s="5">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="K145" s="4" t="s">
         <v>22</v>
@@ -10770,7 +10770,7 @@
         <v>816</v>
       </c>
       <c r="J146" s="2">
-        <v>268</v>
+        <v>249</v>
       </c>
       <c r="K146" s="4" t="s">
         <v>22</v>
@@ -10811,7 +10811,7 @@
         <v>820</v>
       </c>
       <c r="J147" s="5">
-        <v>269</v>
+        <v>292</v>
       </c>
       <c r="K147" s="4" t="s">
         <v>22</v>
@@ -10852,7 +10852,7 @@
         <v>824</v>
       </c>
       <c r="J148" s="2">
-        <v>265</v>
+        <v>285</v>
       </c>
       <c r="K148" s="4" t="s">
         <v>22</v>
@@ -10893,7 +10893,7 @@
         <v>828</v>
       </c>
       <c r="J149" s="5">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="K149" s="4" t="s">
         <v>22</v>
@@ -10934,7 +10934,7 @@
         <v>832</v>
       </c>
       <c r="J150" s="2">
-        <v>260</v>
+        <v>241</v>
       </c>
       <c r="K150" s="4" t="s">
         <v>22</v>
@@ -10975,7 +10975,7 @@
         <v>836</v>
       </c>
       <c r="J151" s="5">
-        <v>253</v>
+        <v>288</v>
       </c>
       <c r="K151" s="4" t="s">
         <v>22</v>
@@ -11016,7 +11016,7 @@
         <v>840</v>
       </c>
       <c r="J152" s="2">
-        <v>255</v>
+        <v>279</v>
       </c>
       <c r="K152" s="4" t="s">
         <v>22</v>
@@ -11057,7 +11057,7 @@
         <v>844</v>
       </c>
       <c r="J153" s="5">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="K153" s="4" t="s">
         <v>22</v>
@@ -11098,7 +11098,7 @@
         <v>848</v>
       </c>
       <c r="J154" s="2">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="K154" s="4" t="s">
         <v>22</v>
@@ -11139,7 +11139,7 @@
         <v>852</v>
       </c>
       <c r="J155" s="5">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="K155" s="4" t="s">
         <v>22</v>
@@ -11180,7 +11180,7 @@
         <v>856</v>
       </c>
       <c r="J156" s="2">
-        <v>298</v>
+        <v>248</v>
       </c>
       <c r="K156" s="4" t="s">
         <v>22</v>
@@ -11221,7 +11221,7 @@
         <v>860</v>
       </c>
       <c r="J157" s="5">
-        <v>278</v>
+        <v>290</v>
       </c>
       <c r="K157" s="4" t="s">
         <v>22</v>
@@ -11262,7 +11262,7 @@
         <v>864</v>
       </c>
       <c r="J158" s="2">
-        <v>293</v>
+        <v>266</v>
       </c>
       <c r="K158" s="4" t="s">
         <v>22</v>
@@ -11303,7 +11303,7 @@
         <v>868</v>
       </c>
       <c r="J159" s="5">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="K159" s="4" t="s">
         <v>22</v>
@@ -11344,7 +11344,7 @@
         <v>872</v>
       </c>
       <c r="J160" s="2">
-        <v>299</v>
+        <v>255</v>
       </c>
       <c r="K160" s="4" t="s">
         <v>22</v>
@@ -11385,7 +11385,7 @@
         <v>876</v>
       </c>
       <c r="J161" s="5">
-        <v>294</v>
+        <v>281</v>
       </c>
       <c r="K161" s="4" t="s">
         <v>22</v>
@@ -11426,7 +11426,7 @@
         <v>880</v>
       </c>
       <c r="J162" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="K162" s="4" t="s">
         <v>22</v>
@@ -11467,7 +11467,7 @@
         <v>884</v>
       </c>
       <c r="J163" s="5">
-        <v>296</v>
+        <v>251</v>
       </c>
       <c r="K163" s="4" t="s">
         <v>22</v>
@@ -11508,7 +11508,7 @@
         <v>888</v>
       </c>
       <c r="J164" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="K164" s="4" t="s">
         <v>22</v>
@@ -11549,7 +11549,7 @@
         <v>892</v>
       </c>
       <c r="J165" s="5">
-        <v>245</v>
+        <v>267</v>
       </c>
       <c r="K165" s="4" t="s">
         <v>22</v>
@@ -11590,7 +11590,7 @@
         <v>896</v>
       </c>
       <c r="J166" s="2">
-        <v>270</v>
+        <v>257</v>
       </c>
       <c r="K166" s="4" t="s">
         <v>22</v>
@@ -11631,7 +11631,7 @@
         <v>900</v>
       </c>
       <c r="J167" s="5">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="K167" s="4" t="s">
         <v>22</v>
@@ -11672,7 +11672,7 @@
         <v>904</v>
       </c>
       <c r="J168" s="2">
-        <v>249</v>
+        <v>275</v>
       </c>
       <c r="K168" s="4" t="s">
         <v>22</v>
@@ -11713,7 +11713,7 @@
         <v>908</v>
       </c>
       <c r="J169" s="5">
-        <v>254</v>
+        <v>288</v>
       </c>
       <c r="K169" s="4" t="s">
         <v>22</v>
@@ -11754,7 +11754,7 @@
         <v>912</v>
       </c>
       <c r="J170" s="2">
-        <v>294</v>
+        <v>278</v>
       </c>
       <c r="K170" s="4" t="s">
         <v>22</v>
@@ -11795,7 +11795,7 @@
         <v>916</v>
       </c>
       <c r="J171" s="5">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="K171" s="4" t="s">
         <v>22</v>
@@ -11836,7 +11836,7 @@
         <v>920</v>
       </c>
       <c r="J172" s="2">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="K172" s="4" t="s">
         <v>22</v>
@@ -11877,7 +11877,7 @@
         <v>924</v>
       </c>
       <c r="J173" s="5">
-        <v>290</v>
+        <v>264</v>
       </c>
       <c r="K173" s="4" t="s">
         <v>22</v>
@@ -11918,7 +11918,7 @@
         <v>928</v>
       </c>
       <c r="J174" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="K174" s="4" t="s">
         <v>22</v>
@@ -11959,7 +11959,7 @@
         <v>932</v>
       </c>
       <c r="J175" s="5">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="K175" s="4" t="s">
         <v>22</v>
@@ -12000,7 +12000,7 @@
         <v>936</v>
       </c>
       <c r="J176" s="2">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="K176" s="4" t="s">
         <v>22</v>
@@ -12041,7 +12041,7 @@
         <v>940</v>
       </c>
       <c r="J177" s="5">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="K177" s="4" t="s">
         <v>22</v>
@@ -12082,7 +12082,7 @@
         <v>944</v>
       </c>
       <c r="J178" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="K178" s="4" t="s">
         <v>22</v>
@@ -12123,7 +12123,7 @@
         <v>948</v>
       </c>
       <c r="J179" s="5">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="K179" s="4" t="s">
         <v>22</v>
@@ -12164,7 +12164,7 @@
         <v>952</v>
       </c>
       <c r="J180" s="2">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="K180" s="4" t="s">
         <v>22</v>
@@ -12205,7 +12205,7 @@
         <v>956</v>
       </c>
       <c r="J181" s="5">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K181" s="4" t="s">
         <v>22</v>
@@ -12246,7 +12246,7 @@
         <v>960</v>
       </c>
       <c r="J182" s="2">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="K182" s="4" t="s">
         <v>22</v>
@@ -12287,7 +12287,7 @@
         <v>964</v>
       </c>
       <c r="J183" s="5">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="K183" s="4" t="s">
         <v>22</v>
@@ -12328,7 +12328,7 @@
         <v>968</v>
       </c>
       <c r="J184" s="2">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="K184" s="4" t="s">
         <v>22</v>
@@ -12369,7 +12369,7 @@
         <v>972</v>
       </c>
       <c r="J185" s="5">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="K185" s="4" t="s">
         <v>22</v>
@@ -12410,7 +12410,7 @@
         <v>976</v>
       </c>
       <c r="J186" s="2">
-        <v>298</v>
+        <v>280</v>
       </c>
       <c r="K186" s="4" t="s">
         <v>22</v>
@@ -12451,7 +12451,7 @@
         <v>980</v>
       </c>
       <c r="J187" s="5">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K187" s="4" t="s">
         <v>22</v>
@@ -12492,7 +12492,7 @@
         <v>984</v>
       </c>
       <c r="J188" s="2">
-        <v>280</v>
+        <v>267</v>
       </c>
       <c r="K188" s="4" t="s">
         <v>22</v>
@@ -12533,7 +12533,7 @@
         <v>988</v>
       </c>
       <c r="J189" s="5">
-        <v>241</v>
+        <v>291</v>
       </c>
       <c r="K189" s="4" t="s">
         <v>22</v>
@@ -12574,7 +12574,7 @@
         <v>992</v>
       </c>
       <c r="J190" s="2">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="K190" s="4" t="s">
         <v>22</v>
@@ -12615,7 +12615,7 @@
         <v>996</v>
       </c>
       <c r="J191" s="5">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="K191" s="4" t="s">
         <v>22</v>
@@ -12656,7 +12656,7 @@
         <v>1000</v>
       </c>
       <c r="J192" s="2">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="K192" s="4" t="s">
         <v>22</v>
@@ -12697,7 +12697,7 @@
         <v>1004</v>
       </c>
       <c r="J193" s="5">
-        <v>243</v>
+        <v>288</v>
       </c>
       <c r="K193" s="4" t="s">
         <v>22</v>
@@ -12738,7 +12738,7 @@
         <v>1008</v>
       </c>
       <c r="J194" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="K194" s="4" t="s">
         <v>22</v>
@@ -12779,7 +12779,7 @@
         <v>1012</v>
       </c>
       <c r="J195" s="5">
-        <v>270</v>
+        <v>245</v>
       </c>
       <c r="K195" s="4" t="s">
         <v>22</v>
@@ -12820,7 +12820,7 @@
         <v>1016</v>
       </c>
       <c r="J196" s="2">
-        <v>288</v>
+        <v>245</v>
       </c>
       <c r="K196" s="4" t="s">
         <v>22</v>
@@ -12861,7 +12861,7 @@
         <v>1020</v>
       </c>
       <c r="J197" s="5">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="K197" s="4" t="s">
         <v>22</v>
@@ -12902,7 +12902,7 @@
         <v>1024</v>
       </c>
       <c r="J198" s="2">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="K198" s="4" t="s">
         <v>22</v>
@@ -12943,7 +12943,7 @@
         <v>1028</v>
       </c>
       <c r="J199" s="5">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="K199" s="4" t="s">
         <v>22</v>
@@ -12984,7 +12984,7 @@
         <v>1032</v>
       </c>
       <c r="J200" s="2">
-        <v>244</v>
+        <v>272</v>
       </c>
       <c r="K200" s="4" t="s">
         <v>22</v>
@@ -13025,7 +13025,7 @@
         <v>1036</v>
       </c>
       <c r="J201" s="5">
-        <v>266</v>
+        <v>252</v>
       </c>
       <c r="K201" s="4" t="s">
         <v>22</v>
@@ -13066,7 +13066,7 @@
         <v>1040</v>
       </c>
       <c r="J202" s="2">
-        <v>267</v>
+        <v>314</v>
       </c>
       <c r="K202" s="4" t="s">
         <v>22</v>
@@ -13107,7 +13107,7 @@
         <v>1044</v>
       </c>
       <c r="J203" s="5">
-        <v>267</v>
+        <v>307</v>
       </c>
       <c r="K203" s="4" t="s">
         <v>22</v>
@@ -13148,7 +13148,7 @@
         <v>1048</v>
       </c>
       <c r="J204" s="2">
-        <v>312</v>
+        <v>265</v>
       </c>
       <c r="K204" s="4" t="s">
         <v>22</v>
@@ -13189,7 +13189,7 @@
         <v>1052</v>
       </c>
       <c r="J205" s="5">
-        <v>285</v>
+        <v>318</v>
       </c>
       <c r="K205" s="4" t="s">
         <v>22</v>
@@ -13230,7 +13230,7 @@
         <v>1056</v>
       </c>
       <c r="J206" s="2">
-        <v>271</v>
+        <v>291</v>
       </c>
       <c r="K206" s="4" t="s">
         <v>22</v>
@@ -13271,7 +13271,7 @@
         <v>1060</v>
       </c>
       <c r="J207" s="5">
-        <v>269</v>
+        <v>310</v>
       </c>
       <c r="K207" s="4" t="s">
         <v>22</v>
@@ -13312,7 +13312,7 @@
         <v>1064</v>
       </c>
       <c r="J208" s="2">
-        <v>296</v>
+        <v>317</v>
       </c>
       <c r="K208" s="4" t="s">
         <v>22</v>
@@ -13353,7 +13353,7 @@
         <v>1068</v>
       </c>
       <c r="J209" s="5">
-        <v>312</v>
+        <v>292</v>
       </c>
       <c r="K209" s="4" t="s">
         <v>22</v>
@@ -13394,7 +13394,7 @@
         <v>1072</v>
       </c>
       <c r="J210" s="2">
-        <v>316</v>
+        <v>268</v>
       </c>
       <c r="K210" s="4" t="s">
         <v>22</v>
@@ -13435,7 +13435,7 @@
         <v>1076</v>
       </c>
       <c r="J211" s="5">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="K211" s="4" t="s">
         <v>22</v>
@@ -13476,7 +13476,7 @@
         <v>1080</v>
       </c>
       <c r="J212" s="2">
-        <v>271</v>
+        <v>306</v>
       </c>
       <c r="K212" s="4" t="s">
         <v>22</v>
@@ -13517,7 +13517,7 @@
         <v>1084</v>
       </c>
       <c r="J213" s="5">
-        <v>306</v>
+        <v>271</v>
       </c>
       <c r="K213" s="4" t="s">
         <v>22</v>
@@ -13558,7 +13558,7 @@
         <v>1088</v>
       </c>
       <c r="J214" s="2">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="K214" s="4" t="s">
         <v>22</v>
@@ -13640,7 +13640,7 @@
         <v>1096</v>
       </c>
       <c r="J216" s="2">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="K216" s="4" t="s">
         <v>22</v>
@@ -13681,7 +13681,7 @@
         <v>1100</v>
       </c>
       <c r="J217" s="5">
-        <v>285</v>
+        <v>304</v>
       </c>
       <c r="K217" s="4" t="s">
         <v>22</v>
@@ -13722,7 +13722,7 @@
         <v>1104</v>
       </c>
       <c r="J218" s="2">
-        <v>318</v>
+        <v>264</v>
       </c>
       <c r="K218" s="4" t="s">
         <v>22</v>
@@ -13763,7 +13763,7 @@
         <v>1108</v>
       </c>
       <c r="J219" s="5">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="K219" s="4" t="s">
         <v>22</v>
@@ -13804,7 +13804,7 @@
         <v>1112</v>
       </c>
       <c r="J220" s="2">
-        <v>317</v>
+        <v>264</v>
       </c>
       <c r="K220" s="4" t="s">
         <v>22</v>
@@ -13845,7 +13845,7 @@
         <v>1116</v>
       </c>
       <c r="J221" s="5">
-        <v>317</v>
+        <v>262</v>
       </c>
       <c r="K221" s="4" t="s">
         <v>22</v>
@@ -13886,7 +13886,7 @@
         <v>1120</v>
       </c>
       <c r="J222" s="2">
-        <v>319</v>
+        <v>296</v>
       </c>
       <c r="K222" s="4" t="s">
         <v>22</v>
@@ -13927,7 +13927,7 @@
         <v>1124</v>
       </c>
       <c r="J223" s="5">
-        <v>275</v>
+        <v>319</v>
       </c>
       <c r="K223" s="4" t="s">
         <v>22</v>
@@ -13968,7 +13968,7 @@
         <v>1128</v>
       </c>
       <c r="J224" s="2">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="K224" s="4" t="s">
         <v>22</v>
@@ -14009,7 +14009,7 @@
         <v>1132</v>
       </c>
       <c r="J225" s="5">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="K225" s="4" t="s">
         <v>22</v>
@@ -14050,7 +14050,7 @@
         <v>1136</v>
       </c>
       <c r="J226" s="2">
-        <v>310</v>
+        <v>294</v>
       </c>
       <c r="K226" s="4" t="s">
         <v>22</v>
@@ -14091,7 +14091,7 @@
         <v>1140</v>
       </c>
       <c r="J227" s="5">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="K227" s="4" t="s">
         <v>22</v>
@@ -14132,7 +14132,7 @@
         <v>1144</v>
       </c>
       <c r="J228" s="2">
-        <v>267</v>
+        <v>291</v>
       </c>
       <c r="K228" s="4" t="s">
         <v>22</v>
@@ -14173,7 +14173,7 @@
         <v>1148</v>
       </c>
       <c r="J229" s="5">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="K229" s="4" t="s">
         <v>22</v>
@@ -14214,7 +14214,7 @@
         <v>1152</v>
       </c>
       <c r="J230" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K230" s="4" t="s">
         <v>22</v>
@@ -14255,7 +14255,7 @@
         <v>1156</v>
       </c>
       <c r="J231" s="5">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="K231" s="4" t="s">
         <v>22</v>
@@ -14296,7 +14296,7 @@
         <v>1160</v>
       </c>
       <c r="J232" s="2">
-        <v>316</v>
+        <v>276</v>
       </c>
       <c r="K232" s="4" t="s">
         <v>22</v>
@@ -14337,7 +14337,7 @@
         <v>1164</v>
       </c>
       <c r="J233" s="5">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="K233" s="4" t="s">
         <v>22</v>
@@ -14378,7 +14378,7 @@
         <v>1168</v>
       </c>
       <c r="J234" s="2">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="K234" s="4" t="s">
         <v>22</v>
@@ -14419,7 +14419,7 @@
         <v>1172</v>
       </c>
       <c r="J235" s="5">
-        <v>263</v>
+        <v>287</v>
       </c>
       <c r="K235" s="4" t="s">
         <v>22</v>
@@ -14460,7 +14460,7 @@
         <v>1176</v>
       </c>
       <c r="J236" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="K236" s="4" t="s">
         <v>22</v>
@@ -14501,7 +14501,7 @@
         <v>1180</v>
       </c>
       <c r="J237" s="5">
-        <v>261</v>
+        <v>287</v>
       </c>
       <c r="K237" s="4" t="s">
         <v>22</v>
@@ -14542,7 +14542,7 @@
         <v>1184</v>
       </c>
       <c r="J238" s="2">
-        <v>262</v>
+        <v>294</v>
       </c>
       <c r="K238" s="4" t="s">
         <v>22</v>
@@ -14583,7 +14583,7 @@
         <v>1188</v>
       </c>
       <c r="J239" s="5">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="K239" s="4" t="s">
         <v>22</v>
@@ -14624,7 +14624,7 @@
         <v>1192</v>
       </c>
       <c r="J240" s="2">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="K240" s="4" t="s">
         <v>22</v>
@@ -14706,7 +14706,7 @@
         <v>1200</v>
       </c>
       <c r="J242" s="2">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="K242" s="4" t="s">
         <v>22</v>
@@ -14747,7 +14747,7 @@
         <v>1204</v>
       </c>
       <c r="J243" s="5">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="K243" s="4" t="s">
         <v>22</v>
@@ -14788,7 +14788,7 @@
         <v>1208</v>
       </c>
       <c r="J244" s="2">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="K244" s="4" t="s">
         <v>22</v>
@@ -14829,7 +14829,7 @@
         <v>1212</v>
       </c>
       <c r="J245" s="5">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K245" s="4" t="s">
         <v>22</v>
@@ -14870,7 +14870,7 @@
         <v>1216</v>
       </c>
       <c r="J246" s="2">
-        <v>266</v>
+        <v>296</v>
       </c>
       <c r="K246" s="4" t="s">
         <v>22</v>
@@ -14911,7 +14911,7 @@
         <v>1220</v>
       </c>
       <c r="J247" s="5">
-        <v>264</v>
+        <v>283</v>
       </c>
       <c r="K247" s="4" t="s">
         <v>22</v>
@@ -14952,7 +14952,7 @@
         <v>1224</v>
       </c>
       <c r="J248" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="K248" s="4" t="s">
         <v>22</v>
@@ -14993,7 +14993,7 @@
         <v>1228</v>
       </c>
       <c r="J249" s="5">
-        <v>307</v>
+        <v>268</v>
       </c>
       <c r="K249" s="4" t="s">
         <v>22</v>
@@ -15034,7 +15034,7 @@
         <v>1232</v>
       </c>
       <c r="J250" s="2">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="K250" s="4" t="s">
         <v>22</v>
@@ -15075,7 +15075,7 @@
         <v>1236</v>
       </c>
       <c r="J251" s="5">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="K251" s="4" t="s">
         <v>22</v>
@@ -15116,7 +15116,7 @@
         <v>1240</v>
       </c>
       <c r="J252" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="K252" s="4" t="s">
         <v>22</v>
@@ -15157,7 +15157,7 @@
         <v>1244</v>
       </c>
       <c r="J253" s="5">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="K253" s="4" t="s">
         <v>22</v>
@@ -15198,7 +15198,7 @@
         <v>1248</v>
       </c>
       <c r="J254" s="2">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="K254" s="4" t="s">
         <v>22</v>
@@ -15239,7 +15239,7 @@
         <v>1252</v>
       </c>
       <c r="J255" s="5">
-        <v>312</v>
+        <v>279</v>
       </c>
       <c r="K255" s="4" t="s">
         <v>22</v>
@@ -15280,7 +15280,7 @@
         <v>1256</v>
       </c>
       <c r="J256" s="2">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="K256" s="4" t="s">
         <v>22</v>
@@ -15321,7 +15321,7 @@
         <v>1260</v>
       </c>
       <c r="J257" s="5">
-        <v>270</v>
+        <v>315</v>
       </c>
       <c r="K257" s="4" t="s">
         <v>22</v>
@@ -15362,7 +15362,7 @@
         <v>1264</v>
       </c>
       <c r="J258" s="2">
-        <v>286</v>
+        <v>310</v>
       </c>
       <c r="K258" s="4" t="s">
         <v>22</v>
@@ -15403,7 +15403,7 @@
         <v>1268</v>
       </c>
       <c r="J259" s="5">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="K259" s="4" t="s">
         <v>22</v>
@@ -15444,7 +15444,7 @@
         <v>1272</v>
       </c>
       <c r="J260" s="2">
-        <v>318</v>
+        <v>279</v>
       </c>
       <c r="K260" s="4" t="s">
         <v>22</v>
@@ -15485,7 +15485,7 @@
         <v>1276</v>
       </c>
       <c r="J261" s="5">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="K261" s="4" t="s">
         <v>22</v>
@@ -15526,7 +15526,7 @@
         <v>1280</v>
       </c>
       <c r="J262" s="2">
-        <v>268</v>
+        <v>304</v>
       </c>
       <c r="K262" s="4" t="s">
         <v>22</v>
@@ -15567,7 +15567,7 @@
         <v>1284</v>
       </c>
       <c r="J263" s="5">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="K263" s="4" t="s">
         <v>22</v>
@@ -15608,7 +15608,7 @@
         <v>1288</v>
       </c>
       <c r="J264" s="2">
-        <v>269</v>
+        <v>302</v>
       </c>
       <c r="K264" s="4" t="s">
         <v>22</v>
@@ -15649,7 +15649,7 @@
         <v>1292</v>
       </c>
       <c r="J265" s="5">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="K265" s="4" t="s">
         <v>22</v>
@@ -15690,7 +15690,7 @@
         <v>1296</v>
       </c>
       <c r="J266" s="2">
-        <v>269</v>
+        <v>309</v>
       </c>
       <c r="K266" s="4" t="s">
         <v>22</v>
@@ -15731,7 +15731,7 @@
         <v>1300</v>
       </c>
       <c r="J267" s="5">
-        <v>279</v>
+        <v>316</v>
       </c>
       <c r="K267" s="4" t="s">
         <v>22</v>
@@ -15772,7 +15772,7 @@
         <v>1304</v>
       </c>
       <c r="J268" s="2">
-        <v>295</v>
+        <v>278</v>
       </c>
       <c r="K268" s="4" t="s">
         <v>22</v>
@@ -15813,7 +15813,7 @@
         <v>1308</v>
       </c>
       <c r="J269" s="5">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="K269" s="4" t="s">
         <v>22</v>
@@ -15854,7 +15854,7 @@
         <v>1312</v>
       </c>
       <c r="J270" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K270" s="4" t="s">
         <v>22</v>
@@ -15895,7 +15895,7 @@
         <v>1316</v>
       </c>
       <c r="J271" s="5">
-        <v>318</v>
+        <v>272</v>
       </c>
       <c r="K271" s="4" t="s">
         <v>22</v>
@@ -15936,7 +15936,7 @@
         <v>1320</v>
       </c>
       <c r="J272" s="2">
-        <v>271</v>
+        <v>296</v>
       </c>
       <c r="K272" s="4" t="s">
         <v>22</v>
@@ -15977,7 +15977,7 @@
         <v>1324</v>
       </c>
       <c r="J273" s="5">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="K273" s="4" t="s">
         <v>22</v>
@@ -16059,7 +16059,7 @@
         <v>1332</v>
       </c>
       <c r="J275" s="5">
-        <v>304</v>
+        <v>269</v>
       </c>
       <c r="K275" s="4" t="s">
         <v>22</v>
@@ -16100,7 +16100,7 @@
         <v>1336</v>
       </c>
       <c r="J276" s="2">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="K276" s="4" t="s">
         <v>22</v>
@@ -16141,7 +16141,7 @@
         <v>1340</v>
       </c>
       <c r="J277" s="5">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="K277" s="4" t="s">
         <v>22</v>
@@ -16182,7 +16182,7 @@
         <v>1344</v>
       </c>
       <c r="J278" s="2">
-        <v>318</v>
+        <v>270</v>
       </c>
       <c r="K278" s="4" t="s">
         <v>22</v>
@@ -16223,7 +16223,7 @@
         <v>1348</v>
       </c>
       <c r="J279" s="5">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="K279" s="4" t="s">
         <v>22</v>
@@ -16264,7 +16264,7 @@
         <v>1352</v>
       </c>
       <c r="J280" s="2">
-        <v>316</v>
+        <v>305</v>
       </c>
       <c r="K280" s="4" t="s">
         <v>22</v>
@@ -16305,7 +16305,7 @@
         <v>1356</v>
       </c>
       <c r="J281" s="5">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="K281" s="4" t="s">
         <v>22</v>
@@ -16346,7 +16346,7 @@
         <v>1360</v>
       </c>
       <c r="J282" s="2">
-        <v>296</v>
+        <v>309</v>
       </c>
       <c r="K282" s="4" t="s">
         <v>22</v>
@@ -16387,7 +16387,7 @@
         <v>1364</v>
       </c>
       <c r="J283" s="5">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="K283" s="4" t="s">
         <v>22</v>
@@ -16428,7 +16428,7 @@
         <v>1368</v>
       </c>
       <c r="J284" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="K284" s="4" t="s">
         <v>22</v>
@@ -16469,7 +16469,7 @@
         <v>1372</v>
       </c>
       <c r="J285" s="5">
-        <v>314</v>
+        <v>277</v>
       </c>
       <c r="K285" s="4" t="s">
         <v>22</v>
@@ -16510,7 +16510,7 @@
         <v>1376</v>
       </c>
       <c r="J286" s="2">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="K286" s="4" t="s">
         <v>22</v>
@@ -16551,7 +16551,7 @@
         <v>1380</v>
       </c>
       <c r="J287" s="5">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="K287" s="4" t="s">
         <v>22</v>
@@ -16592,7 +16592,7 @@
         <v>1384</v>
       </c>
       <c r="J288" s="2">
-        <v>270</v>
+        <v>299</v>
       </c>
       <c r="K288" s="4" t="s">
         <v>22</v>
@@ -16633,7 +16633,7 @@
         <v>1388</v>
       </c>
       <c r="J289" s="5">
-        <v>270</v>
+        <v>314</v>
       </c>
       <c r="K289" s="4" t="s">
         <v>22</v>
@@ -16674,7 +16674,7 @@
         <v>1392</v>
       </c>
       <c r="J290" s="2">
-        <v>266</v>
+        <v>286</v>
       </c>
       <c r="K290" s="4" t="s">
         <v>22</v>
@@ -16715,7 +16715,7 @@
         <v>1396</v>
       </c>
       <c r="J291" s="5">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="K291" s="4" t="s">
         <v>22</v>
@@ -16756,7 +16756,7 @@
         <v>1400</v>
       </c>
       <c r="J292" s="2">
-        <v>287</v>
+        <v>264</v>
       </c>
       <c r="K292" s="4" t="s">
         <v>22</v>
@@ -16797,7 +16797,7 @@
         <v>1404</v>
       </c>
       <c r="J293" s="5">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="K293" s="4" t="s">
         <v>22</v>
@@ -16838,7 +16838,7 @@
         <v>1408</v>
       </c>
       <c r="J294" s="2">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="K294" s="4" t="s">
         <v>22</v>
@@ -16920,7 +16920,7 @@
         <v>1416</v>
       </c>
       <c r="J296" s="2">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="K296" s="4" t="s">
         <v>22</v>
@@ -16961,7 +16961,7 @@
         <v>1420</v>
       </c>
       <c r="J297" s="5">
-        <v>305</v>
+        <v>260</v>
       </c>
       <c r="K297" s="4" t="s">
         <v>22</v>
@@ -17002,7 +17002,7 @@
         <v>1424</v>
       </c>
       <c r="J298" s="2">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="K298" s="4" t="s">
         <v>22</v>
@@ -17043,7 +17043,7 @@
         <v>1428</v>
       </c>
       <c r="J299" s="5">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="K299" s="4" t="s">
         <v>22</v>
@@ -17084,7 +17084,7 @@
         <v>1432</v>
       </c>
       <c r="J300" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="K300" s="4" t="s">
         <v>22</v>
@@ -17125,7 +17125,7 @@
         <v>1436</v>
       </c>
       <c r="J301" s="5">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="K301" s="4" t="s">
         <v>22</v>
